--- a/Predictions/timestamps_cp_cnn.xlsx
+++ b/Predictions/timestamps_cp_cnn.xlsx
@@ -462,4082 +462,4082 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>37.45269012451172</v>
+        <v>38.17903900146484</v>
       </c>
       <c r="B2" t="n">
-        <v>37.45269012451172</v>
+        <v>38.17903900146484</v>
       </c>
       <c r="C2" t="n">
-        <v>37.45269012451172</v>
+        <v>38.17903900146484</v>
       </c>
       <c r="D2" t="n">
-        <v>37.45269012451172</v>
+        <v>38.17903900146484</v>
       </c>
       <c r="E2" t="n">
-        <v>37.45269012451172</v>
+        <v>38.17903900146484</v>
       </c>
       <c r="F2" t="n">
-        <v>37.45269012451172</v>
+        <v>38.17903900146484</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>40.31965255737305</v>
+        <v>26.86281204223633</v>
       </c>
       <c r="B3" t="n">
-        <v>35.53824996948242</v>
+        <v>32.82307052612305</v>
       </c>
       <c r="C3" t="n">
-        <v>12.23263072967529</v>
+        <v>4.444085121154785</v>
       </c>
       <c r="D3" t="n">
-        <v>14.2158374786377</v>
+        <v>17.49151611328125</v>
       </c>
       <c r="E3" t="n">
-        <v>-19.59043502807617</v>
+        <v>-12.13683319091797</v>
       </c>
       <c r="F3" t="n">
-        <v>-19.68183898925781</v>
+        <v>-17.25821685791016</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>44.94857025146484</v>
+        <v>32.61988067626953</v>
       </c>
       <c r="B4" t="n">
-        <v>35.24908828735352</v>
+        <v>31.00729560852051</v>
       </c>
       <c r="C4" t="n">
-        <v>13.15682601928711</v>
+        <v>7.936610221862793</v>
       </c>
       <c r="D4" t="n">
-        <v>20.82697677612305</v>
+        <v>21.3259162902832</v>
       </c>
       <c r="E4" t="n">
-        <v>-14.72552013397217</v>
+        <v>-14.22215366363525</v>
       </c>
       <c r="F4" t="n">
-        <v>-17.48292922973633</v>
+        <v>-15.79000282287598</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>45.53506088256836</v>
+        <v>27.21063041687012</v>
       </c>
       <c r="B5" t="n">
-        <v>34.83913040161133</v>
+        <v>31.29547309875488</v>
       </c>
       <c r="C5" t="n">
-        <v>16.59051132202148</v>
+        <v>8.024340629577637</v>
       </c>
       <c r="D5" t="n">
-        <v>17.52516937255859</v>
+        <v>19.53195571899414</v>
       </c>
       <c r="E5" t="n">
-        <v>-19.00230979919434</v>
+        <v>-13.71575832366943</v>
       </c>
       <c r="F5" t="n">
-        <v>-15.82143783569336</v>
+        <v>-13.92905235290527</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>41.72540283203125</v>
+        <v>29.80391883850098</v>
       </c>
       <c r="B6" t="n">
-        <v>25.02775955200195</v>
+        <v>34.29644775390625</v>
       </c>
       <c r="C6" t="n">
-        <v>21.30092620849609</v>
+        <v>4.878823280334473</v>
       </c>
       <c r="D6" t="n">
-        <v>18.33954238891602</v>
+        <v>18.58999443054199</v>
       </c>
       <c r="E6" t="n">
-        <v>-17.42875289916992</v>
+        <v>-11.479660987854</v>
       </c>
       <c r="F6" t="n">
-        <v>-21.26569557189941</v>
+        <v>-11.9329776763916</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>35.91081237792969</v>
+        <v>27.70675277709961</v>
       </c>
       <c r="B7" t="n">
-        <v>29.25567626953125</v>
+        <v>31.40976333618164</v>
       </c>
       <c r="C7" t="n">
-        <v>28.37674522399902</v>
+        <v>5.333840370178223</v>
       </c>
       <c r="D7" t="n">
-        <v>17.51395606994629</v>
+        <v>17.40459060668945</v>
       </c>
       <c r="E7" t="n">
-        <v>-15.853590965271</v>
+        <v>-12.20536804199219</v>
       </c>
       <c r="F7" t="n">
-        <v>-15.20963001251221</v>
+        <v>-12.76809501647949</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>36.34413528442383</v>
+        <v>25.87044906616211</v>
       </c>
       <c r="B8" t="n">
-        <v>26.31573867797852</v>
+        <v>33.94862365722656</v>
       </c>
       <c r="C8" t="n">
-        <v>14.11337757110596</v>
+        <v>5.641268730163574</v>
       </c>
       <c r="D8" t="n">
-        <v>19.84812927246094</v>
+        <v>17.06396484375</v>
       </c>
       <c r="E8" t="n">
-        <v>-12.97408008575439</v>
+        <v>-15.91245651245117</v>
       </c>
       <c r="F8" t="n">
-        <v>-14.03752899169922</v>
+        <v>-11.83891868591309</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>39.358642578125</v>
+        <v>24.1733512878418</v>
       </c>
       <c r="B9" t="n">
-        <v>26.25963973999023</v>
+        <v>29.77989387512207</v>
       </c>
       <c r="C9" t="n">
-        <v>16.75308990478516</v>
+        <v>5.424674034118652</v>
       </c>
       <c r="D9" t="n">
-        <v>13.73143100738525</v>
+        <v>19.88665771484375</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.008670806884766</v>
+        <v>-14.42450904846191</v>
       </c>
       <c r="F9" t="n">
-        <v>-9.376434326171875</v>
+        <v>-8.860648155212402</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>30.29337501525879</v>
+        <v>20.4854793548584</v>
       </c>
       <c r="B10" t="n">
-        <v>24.34624481201172</v>
+        <v>30.45695877075195</v>
       </c>
       <c r="C10" t="n">
-        <v>19.05294990539551</v>
+        <v>7.254195213317871</v>
       </c>
       <c r="D10" t="n">
-        <v>14.64286041259766</v>
+        <v>15.95506572723389</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.889055252075195</v>
+        <v>-9.162126541137695</v>
       </c>
       <c r="F10" t="n">
-        <v>-12.98773670196533</v>
+        <v>-6.949033737182617</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>26.13715362548828</v>
+        <v>26.2797794342041</v>
       </c>
       <c r="B11" t="n">
-        <v>26.46437072753906</v>
+        <v>29.49907112121582</v>
       </c>
       <c r="C11" t="n">
-        <v>18.47914505004883</v>
+        <v>6.993861198425293</v>
       </c>
       <c r="D11" t="n">
-        <v>14.12693500518799</v>
+        <v>16.32659530639648</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.057551383972168</v>
+        <v>-13.86011505126953</v>
       </c>
       <c r="F11" t="n">
-        <v>-13.08755016326904</v>
+        <v>-6.765801906585693</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>25.04808807373047</v>
+        <v>26.13456726074219</v>
       </c>
       <c r="B12" t="n">
-        <v>21.54988861083984</v>
+        <v>24.72845268249512</v>
       </c>
       <c r="C12" t="n">
-        <v>11.44209003448486</v>
+        <v>4.076727867126465</v>
       </c>
       <c r="D12" t="n">
-        <v>18.44588851928711</v>
+        <v>14.73680400848389</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.747098922729492</v>
+        <v>-8.988518714904785</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.263570308685303</v>
+        <v>1.495381712913513</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>24.76678466796875</v>
+        <v>24.53326797485352</v>
       </c>
       <c r="B13" t="n">
-        <v>23.27332496643066</v>
+        <v>26.59523773193359</v>
       </c>
       <c r="C13" t="n">
-        <v>17.53492736816406</v>
+        <v>5.267420768737793</v>
       </c>
       <c r="D13" t="n">
-        <v>25.58036041259766</v>
+        <v>16.80728721618652</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.227290630340576</v>
+        <v>-11.86647701263428</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3006940484046936</v>
+        <v>-1.976731419563293</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>23.30288696289062</v>
+        <v>21.76180267333984</v>
       </c>
       <c r="B14" t="n">
-        <v>19.45855331420898</v>
+        <v>22.0490608215332</v>
       </c>
       <c r="C14" t="n">
-        <v>11.87368297576904</v>
+        <v>6.979374885559082</v>
       </c>
       <c r="D14" t="n">
-        <v>21.78629302978516</v>
+        <v>16.19382667541504</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.492722511291504</v>
+        <v>-13.72285747528076</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6449136137962341</v>
+        <v>1.025324702262878</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>21.87905120849609</v>
+        <v>23.19587898254395</v>
       </c>
       <c r="B15" t="n">
-        <v>20.16158485412598</v>
+        <v>25.75523567199707</v>
       </c>
       <c r="C15" t="n">
-        <v>16.99454307556152</v>
+        <v>0.4244583249092102</v>
       </c>
       <c r="D15" t="n">
-        <v>22.56910514831543</v>
+        <v>13.38300704956055</v>
       </c>
       <c r="E15" t="n">
-        <v>1.498042106628418</v>
+        <v>-13.51272773742676</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.531874895095825</v>
+        <v>3.898120880126953</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>17.98845100402832</v>
+        <v>22.13945198059082</v>
       </c>
       <c r="B16" t="n">
-        <v>13.91649913787842</v>
+        <v>21.25967407226562</v>
       </c>
       <c r="C16" t="n">
-        <v>10.91514873504639</v>
+        <v>2.97790789604187</v>
       </c>
       <c r="D16" t="n">
-        <v>25.85209274291992</v>
+        <v>17.87008094787598</v>
       </c>
       <c r="E16" t="n">
-        <v>5.681757926940918</v>
+        <v>-13.55334854125977</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.06806284934282303</v>
+        <v>2.12873649597168</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>12.55837726593018</v>
+        <v>21.1248950958252</v>
       </c>
       <c r="B17" t="n">
-        <v>12.92759799957275</v>
+        <v>22.33662223815918</v>
       </c>
       <c r="C17" t="n">
-        <v>11.30273056030273</v>
+        <v>2.5786292552948</v>
       </c>
       <c r="D17" t="n">
-        <v>16.6959400177002</v>
+        <v>14.77615070343018</v>
       </c>
       <c r="E17" t="n">
-        <v>6.361760139465332</v>
+        <v>-16.3598461151123</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.88982355594635</v>
+        <v>3.806310653686523</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>13.17853927612305</v>
+        <v>20.09025764465332</v>
       </c>
       <c r="B18" t="n">
-        <v>14.83230018615723</v>
+        <v>16.28570938110352</v>
       </c>
       <c r="C18" t="n">
-        <v>8.712258338928223</v>
+        <v>-1.030333638191223</v>
       </c>
       <c r="D18" t="n">
-        <v>18.15629768371582</v>
+        <v>14.38604545593262</v>
       </c>
       <c r="E18" t="n">
-        <v>1.157375335693359</v>
+        <v>-14.26200580596924</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1869639754295349</v>
+        <v>5.572259902954102</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13.97569274902344</v>
+        <v>21.00223541259766</v>
       </c>
       <c r="B19" t="n">
-        <v>13.80130100250244</v>
+        <v>16.8378791809082</v>
       </c>
       <c r="C19" t="n">
-        <v>7.745768547058105</v>
+        <v>1.070187449455261</v>
       </c>
       <c r="D19" t="n">
-        <v>25.72437858581543</v>
+        <v>17.06032180786133</v>
       </c>
       <c r="E19" t="n">
-        <v>7.045454025268555</v>
+        <v>-14.74657344818115</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9969478249549866</v>
+        <v>8.304049491882324</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>11.67677688598633</v>
+        <v>16.10899353027344</v>
       </c>
       <c r="B20" t="n">
-        <v>14.73263072967529</v>
+        <v>18.38242530822754</v>
       </c>
       <c r="C20" t="n">
-        <v>17.51505661010742</v>
+        <v>0.9619491696357727</v>
       </c>
       <c r="D20" t="n">
-        <v>19.88674736022949</v>
+        <v>16.91250419616699</v>
       </c>
       <c r="E20" t="n">
-        <v>9.031039237976074</v>
+        <v>-12.73981380462646</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.587617516517639</v>
+        <v>10.43159103393555</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>9.564927101135254</v>
+        <v>15.77566814422607</v>
       </c>
       <c r="B21" t="n">
-        <v>10.1992826461792</v>
+        <v>15.09177303314209</v>
       </c>
       <c r="C21" t="n">
-        <v>6.218459129333496</v>
+        <v>-2.918534517288208</v>
       </c>
       <c r="D21" t="n">
-        <v>21.07949066162109</v>
+        <v>17.38372230529785</v>
       </c>
       <c r="E21" t="n">
-        <v>13.52275943756104</v>
+        <v>-11.7110652923584</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.23517918586731</v>
+        <v>6.80488395690918</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14.45607662200928</v>
+        <v>9.315674781799316</v>
       </c>
       <c r="B22" t="n">
-        <v>12.12095165252686</v>
+        <v>13.8530216217041</v>
       </c>
       <c r="C22" t="n">
-        <v>10.53856658935547</v>
+        <v>5.594132423400879</v>
       </c>
       <c r="D22" t="n">
-        <v>25.21608924865723</v>
+        <v>14.45716762542725</v>
       </c>
       <c r="E22" t="n">
-        <v>8.082287788391113</v>
+        <v>-8.181972503662109</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.654073238372803</v>
+        <v>6.038787841796875</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5.355562686920166</v>
+        <v>11.16604042053223</v>
       </c>
       <c r="B23" t="n">
-        <v>10.65891075134277</v>
+        <v>14.21883869171143</v>
       </c>
       <c r="C23" t="n">
-        <v>9.940016746520996</v>
+        <v>7.541834831237793</v>
       </c>
       <c r="D23" t="n">
-        <v>24.33213043212891</v>
+        <v>12.18341159820557</v>
       </c>
       <c r="E23" t="n">
-        <v>12.19389820098877</v>
+        <v>-10.44089317321777</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.382302761077881</v>
+        <v>10.7982177734375</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>8.911727905273438</v>
+        <v>9.67031192779541</v>
       </c>
       <c r="B24" t="n">
-        <v>6.074944496154785</v>
+        <v>14.70262432098389</v>
       </c>
       <c r="C24" t="n">
-        <v>14.70618629455566</v>
+        <v>5.505133628845215</v>
       </c>
       <c r="D24" t="n">
-        <v>25.41063117980957</v>
+        <v>15.23974132537842</v>
       </c>
       <c r="E24" t="n">
-        <v>2.802050590515137</v>
+        <v>-13.62825012207031</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.136366844177246</v>
+        <v>1.155865550041199</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5.568817615509033</v>
+        <v>2.989756107330322</v>
       </c>
       <c r="B25" t="n">
-        <v>16.49954795837402</v>
+        <v>13.36740589141846</v>
       </c>
       <c r="C25" t="n">
-        <v>14.68837833404541</v>
+        <v>6.683720588684082</v>
       </c>
       <c r="D25" t="n">
-        <v>27.80900001525879</v>
+        <v>15.85437393188477</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.615248680114746</v>
+        <v>-16.71385765075684</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.08567428588867</v>
+        <v>0.147854745388031</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>8.723795890808105</v>
+        <v>5.907474994659424</v>
       </c>
       <c r="B26" t="n">
-        <v>13.92391109466553</v>
+        <v>11.02738475799561</v>
       </c>
       <c r="C26" t="n">
-        <v>12.87190341949463</v>
+        <v>4.520144462585449</v>
       </c>
       <c r="D26" t="n">
-        <v>25.02975654602051</v>
+        <v>19.00107383728027</v>
       </c>
       <c r="E26" t="n">
-        <v>-13.14065170288086</v>
+        <v>-16.32648658752441</v>
       </c>
       <c r="F26" t="n">
-        <v>-27.54916572570801</v>
+        <v>1.787891268730164</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>9.192728996276855</v>
+        <v>3.386677265167236</v>
       </c>
       <c r="B27" t="n">
-        <v>11.86513805389404</v>
+        <v>14.63142681121826</v>
       </c>
       <c r="C27" t="n">
-        <v>18.08453178405762</v>
+        <v>6.608006477355957</v>
       </c>
       <c r="D27" t="n">
-        <v>32.00483322143555</v>
+        <v>18.84482574462891</v>
       </c>
       <c r="E27" t="n">
-        <v>-19.2778491973877</v>
+        <v>-18.14175224304199</v>
       </c>
       <c r="F27" t="n">
-        <v>-32.7400016784668</v>
+        <v>-6.855643749237061</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>8.014761924743652</v>
+        <v>5.327135562896729</v>
       </c>
       <c r="B28" t="n">
-        <v>18.94298362731934</v>
+        <v>10.29725646972656</v>
       </c>
       <c r="C28" t="n">
-        <v>19.08841705322266</v>
+        <v>12.04292011260986</v>
       </c>
       <c r="D28" t="n">
-        <v>36.89397048950195</v>
+        <v>15.89107322692871</v>
       </c>
       <c r="E28" t="n">
-        <v>-31.83934211730957</v>
+        <v>-21.31953620910645</v>
       </c>
       <c r="F28" t="n">
-        <v>-32.95419311523438</v>
+        <v>-16.68863296508789</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>5.620684146881104</v>
+        <v>5.240284442901611</v>
       </c>
       <c r="B29" t="n">
-        <v>15.07085227966309</v>
+        <v>11.96043872833252</v>
       </c>
       <c r="C29" t="n">
-        <v>20.40121459960938</v>
+        <v>14.86686038970947</v>
       </c>
       <c r="D29" t="n">
-        <v>39.48788070678711</v>
+        <v>26.0345630645752</v>
       </c>
       <c r="E29" t="n">
-        <v>-38.57369232177734</v>
+        <v>-23.57326889038086</v>
       </c>
       <c r="F29" t="n">
-        <v>-37.59700012207031</v>
+        <v>-25.16839981079102</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>15.34508895874023</v>
+        <v>8.404826164245605</v>
       </c>
       <c r="B30" t="n">
-        <v>14.75675868988037</v>
+        <v>8.097922325134277</v>
       </c>
       <c r="C30" t="n">
-        <v>26.48102760314941</v>
+        <v>18.76193618774414</v>
       </c>
       <c r="D30" t="n">
-        <v>47.63796615600586</v>
+        <v>24.3253116607666</v>
       </c>
       <c r="E30" t="n">
-        <v>-41.77360153198242</v>
+        <v>-30.27422904968262</v>
       </c>
       <c r="F30" t="n">
-        <v>-43.23703765869141</v>
+        <v>-35.3560791015625</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>12.69110012054443</v>
+        <v>7.304371356964111</v>
       </c>
       <c r="B31" t="n">
-        <v>19.47892379760742</v>
+        <v>13.9824161529541</v>
       </c>
       <c r="C31" t="n">
-        <v>31.48456192016602</v>
+        <v>25.12442016601562</v>
       </c>
       <c r="D31" t="n">
-        <v>46.97479629516602</v>
+        <v>32.05728530883789</v>
       </c>
       <c r="E31" t="n">
-        <v>-39.73019409179688</v>
+        <v>-34.16861343383789</v>
       </c>
       <c r="F31" t="n">
-        <v>-51.08283615112305</v>
+        <v>-42.22125244140625</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>17.36130332946777</v>
+        <v>12.38808155059814</v>
       </c>
       <c r="B32" t="n">
-        <v>17.94268035888672</v>
+        <v>13.31209468841553</v>
       </c>
       <c r="C32" t="n">
-        <v>38.4615478515625</v>
+        <v>35.7307243347168</v>
       </c>
       <c r="D32" t="n">
-        <v>49.4014892578125</v>
+        <v>38.11756134033203</v>
       </c>
       <c r="E32" t="n">
-        <v>-40.86716461181641</v>
+        <v>-31.13859939575195</v>
       </c>
       <c r="F32" t="n">
-        <v>-57.32112503051758</v>
+        <v>-49.74167251586914</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>18.37128067016602</v>
+        <v>15.67484092712402</v>
       </c>
       <c r="B33" t="n">
-        <v>29.15714836120605</v>
+        <v>18.56085014343262</v>
       </c>
       <c r="C33" t="n">
-        <v>42.6790885925293</v>
+        <v>33.08158493041992</v>
       </c>
       <c r="D33" t="n">
-        <v>54.54030609130859</v>
+        <v>40.30116271972656</v>
       </c>
       <c r="E33" t="n">
-        <v>-42.00576782226562</v>
+        <v>-37.90897369384766</v>
       </c>
       <c r="F33" t="n">
-        <v>-59.83346939086914</v>
+        <v>-49.9537353515625</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>26.61576271057129</v>
+        <v>17.43686294555664</v>
       </c>
       <c r="B34" t="n">
-        <v>22.89181327819824</v>
+        <v>19.52327919006348</v>
       </c>
       <c r="C34" t="n">
-        <v>47.89508056640625</v>
+        <v>40.32751083374023</v>
       </c>
       <c r="D34" t="n">
-        <v>55.1632194519043</v>
+        <v>45.44573211669922</v>
       </c>
       <c r="E34" t="n">
-        <v>-38.75848770141602</v>
+        <v>-36.96226501464844</v>
       </c>
       <c r="F34" t="n">
-        <v>-62.49186706542969</v>
+        <v>-57.60217666625977</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>26.82012557983398</v>
+        <v>17.20061874389648</v>
       </c>
       <c r="B35" t="n">
-        <v>31.54055023193359</v>
+        <v>22.7742977142334</v>
       </c>
       <c r="C35" t="n">
-        <v>48.58567810058594</v>
+        <v>40.67141723632812</v>
       </c>
       <c r="D35" t="n">
-        <v>59.03639221191406</v>
+        <v>52.76216506958008</v>
       </c>
       <c r="E35" t="n">
-        <v>-40.38883209228516</v>
+        <v>-34.99460601806641</v>
       </c>
       <c r="F35" t="n">
-        <v>-51.19635391235352</v>
+        <v>-56.14141464233398</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>32.21549224853516</v>
+        <v>21.6185245513916</v>
       </c>
       <c r="B36" t="n">
-        <v>34.12632369995117</v>
+        <v>24.64842987060547</v>
       </c>
       <c r="C36" t="n">
-        <v>53.1535530090332</v>
+        <v>41.14267730712891</v>
       </c>
       <c r="D36" t="n">
-        <v>56.69530868530273</v>
+        <v>55.97414398193359</v>
       </c>
       <c r="E36" t="n">
-        <v>-35.54184341430664</v>
+        <v>-35.92815780639648</v>
       </c>
       <c r="F36" t="n">
-        <v>-45.95066070556641</v>
+        <v>-47.87343978881836</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>35.59099960327148</v>
+        <v>25.37566566467285</v>
       </c>
       <c r="B37" t="n">
-        <v>34.63078308105469</v>
+        <v>28.46621704101562</v>
       </c>
       <c r="C37" t="n">
-        <v>46.02811813354492</v>
+        <v>46.45328903198242</v>
       </c>
       <c r="D37" t="n">
-        <v>57.04930877685547</v>
+        <v>55.24142456054688</v>
       </c>
       <c r="E37" t="n">
-        <v>-27.66091156005859</v>
+        <v>-27.1874885559082</v>
       </c>
       <c r="F37" t="n">
-        <v>-39.25545883178711</v>
+        <v>-42.06134414672852</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>35.53077697753906</v>
+        <v>27.23398780822754</v>
       </c>
       <c r="B38" t="n">
-        <v>38.76571655273438</v>
+        <v>30.26260566711426</v>
       </c>
       <c r="C38" t="n">
-        <v>36.47297286987305</v>
+        <v>42.99894714355469</v>
       </c>
       <c r="D38" t="n">
-        <v>53.13998031616211</v>
+        <v>51.37507629394531</v>
       </c>
       <c r="E38" t="n">
-        <v>-28.59328079223633</v>
+        <v>-27.12101173400879</v>
       </c>
       <c r="F38" t="n">
-        <v>-37.32601547241211</v>
+        <v>-36.15817642211914</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>33.82222747802734</v>
+        <v>28.78496360778809</v>
       </c>
       <c r="B39" t="n">
-        <v>37.09964370727539</v>
+        <v>35.1479606628418</v>
       </c>
       <c r="C39" t="n">
-        <v>35.00563812255859</v>
+        <v>40.39498138427734</v>
       </c>
       <c r="D39" t="n">
-        <v>47.75964736938477</v>
+        <v>55.98495864868164</v>
       </c>
       <c r="E39" t="n">
-        <v>-26.96238136291504</v>
+        <v>-21.35552215576172</v>
       </c>
       <c r="F39" t="n">
-        <v>-35.50749588012695</v>
+        <v>-31.50681495666504</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>36.244140625</v>
+        <v>33.02290344238281</v>
       </c>
       <c r="B40" t="n">
-        <v>38.98783493041992</v>
+        <v>37.3326416015625</v>
       </c>
       <c r="C40" t="n">
-        <v>41.03255462646484</v>
+        <v>38.0617561340332</v>
       </c>
       <c r="D40" t="n">
-        <v>48.639892578125</v>
+        <v>57.51260757446289</v>
       </c>
       <c r="E40" t="n">
-        <v>-23.69537162780762</v>
+        <v>-21.83041763305664</v>
       </c>
       <c r="F40" t="n">
-        <v>-27.60905265808105</v>
+        <v>-29.59410095214844</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>36.04978179931641</v>
+        <v>37.35701751708984</v>
       </c>
       <c r="B41" t="n">
-        <v>41.44110107421875</v>
+        <v>40.25080108642578</v>
       </c>
       <c r="C41" t="n">
-        <v>30.38046836853027</v>
+        <v>38.1658935546875</v>
       </c>
       <c r="D41" t="n">
-        <v>40.4028205871582</v>
+        <v>54.37590789794922</v>
       </c>
       <c r="E41" t="n">
-        <v>-17.87747955322266</v>
+        <v>-10.81492042541504</v>
       </c>
       <c r="F41" t="n">
-        <v>-28.39926338195801</v>
+        <v>-28.02151298522949</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>33.63146209716797</v>
+        <v>38.24984741210938</v>
       </c>
       <c r="B42" t="n">
-        <v>42.16065979003906</v>
+        <v>37.20284271240234</v>
       </c>
       <c r="C42" t="n">
-        <v>17.01162719726562</v>
+        <v>35.66275787353516</v>
       </c>
       <c r="D42" t="n">
-        <v>38.01351165771484</v>
+        <v>46.5052375793457</v>
       </c>
       <c r="E42" t="n">
-        <v>-14.71523475646973</v>
+        <v>-12.39317321777344</v>
       </c>
       <c r="F42" t="n">
-        <v>-26.55282211303711</v>
+        <v>-24.83787727355957</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>37.45214462280273</v>
+        <v>36.73228454589844</v>
       </c>
       <c r="B43" t="n">
-        <v>38.16409301757812</v>
+        <v>45.54853057861328</v>
       </c>
       <c r="C43" t="n">
-        <v>15.58467578887939</v>
+        <v>27.49724960327148</v>
       </c>
       <c r="D43" t="n">
-        <v>26.41883277893066</v>
+        <v>45.27410888671875</v>
       </c>
       <c r="E43" t="n">
-        <v>-16.58917617797852</v>
+        <v>-7.797657012939453</v>
       </c>
       <c r="F43" t="n">
-        <v>-25.95571517944336</v>
+        <v>-20.68341827392578</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>36.56539916992188</v>
+        <v>40.21876525878906</v>
       </c>
       <c r="B44" t="n">
-        <v>39.06069946289062</v>
+        <v>43.33415985107422</v>
       </c>
       <c r="C44" t="n">
-        <v>14.79965877532959</v>
+        <v>29.97231101989746</v>
       </c>
       <c r="D44" t="n">
-        <v>28.4182243347168</v>
+        <v>40.33257675170898</v>
       </c>
       <c r="E44" t="n">
-        <v>-10.05935573577881</v>
+        <v>-2.26274585723877</v>
       </c>
       <c r="F44" t="n">
-        <v>-22.20625495910645</v>
+        <v>-19.96682548522949</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>36.16626739501953</v>
+        <v>36.87361526489258</v>
       </c>
       <c r="B45" t="n">
-        <v>37.78791427612305</v>
+        <v>44.75948333740234</v>
       </c>
       <c r="C45" t="n">
-        <v>6.087088584899902</v>
+        <v>20.38291931152344</v>
       </c>
       <c r="D45" t="n">
-        <v>20.44890022277832</v>
+        <v>34.53782653808594</v>
       </c>
       <c r="E45" t="n">
-        <v>-12.49162101745605</v>
+        <v>-0.2882914543151855</v>
       </c>
       <c r="F45" t="n">
-        <v>-24.80034828186035</v>
+        <v>-19.17347145080566</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>39.92219924926758</v>
+        <v>46.77812957763672</v>
       </c>
       <c r="B46" t="n">
-        <v>44.07695007324219</v>
+        <v>42.60893249511719</v>
       </c>
       <c r="C46" t="n">
-        <v>7.716044425964355</v>
+        <v>20.48843193054199</v>
       </c>
       <c r="D46" t="n">
-        <v>15.27586460113525</v>
+        <v>31.06986045837402</v>
       </c>
       <c r="E46" t="n">
-        <v>-15.02658081054688</v>
+        <v>-2.70541524887085</v>
       </c>
       <c r="F46" t="n">
-        <v>-21.06229782104492</v>
+        <v>-16.71946716308594</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>36.95083236694336</v>
+        <v>45.71073913574219</v>
       </c>
       <c r="B47" t="n">
-        <v>42.63119125366211</v>
+        <v>40.25759124755859</v>
       </c>
       <c r="C47" t="n">
-        <v>3.720530271530151</v>
+        <v>17.18650436401367</v>
       </c>
       <c r="D47" t="n">
-        <v>9.831723213195801</v>
+        <v>29.6654167175293</v>
       </c>
       <c r="E47" t="n">
-        <v>-13.85836219787598</v>
+        <v>-3.216880798339844</v>
       </c>
       <c r="F47" t="n">
-        <v>-22.54345703125</v>
+        <v>-15.60597801208496</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>40.63206481933594</v>
+        <v>47.45177841186523</v>
       </c>
       <c r="B48" t="n">
-        <v>42.62586212158203</v>
+        <v>44.81769943237305</v>
       </c>
       <c r="C48" t="n">
-        <v>13.07956600189209</v>
+        <v>15.72260093688965</v>
       </c>
       <c r="D48" t="n">
-        <v>5.069207191467285</v>
+        <v>21.62859344482422</v>
       </c>
       <c r="E48" t="n">
-        <v>-17.94192886352539</v>
+        <v>-3.164340972900391</v>
       </c>
       <c r="F48" t="n">
-        <v>-23.46292495727539</v>
+        <v>-19.54506683349609</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>41.55203628540039</v>
+        <v>29.33593559265137</v>
       </c>
       <c r="B49" t="n">
-        <v>39.81073760986328</v>
+        <v>42.67898559570312</v>
       </c>
       <c r="C49" t="n">
-        <v>7.61693286895752</v>
+        <v>8.421330451965332</v>
       </c>
       <c r="D49" t="n">
-        <v>12.11690616607666</v>
+        <v>20.3433895111084</v>
       </c>
       <c r="E49" t="n">
-        <v>-15.82191562652588</v>
+        <v>-5.927853107452393</v>
       </c>
       <c r="F49" t="n">
-        <v>-25.9372730255127</v>
+        <v>-23.10164642333984</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>41.17661285400391</v>
+        <v>27.91205787658691</v>
       </c>
       <c r="B50" t="n">
-        <v>43.37850570678711</v>
+        <v>45.8170280456543</v>
       </c>
       <c r="C50" t="n">
-        <v>4.95815372467041</v>
+        <v>9.680146217346191</v>
       </c>
       <c r="D50" t="n">
-        <v>2.763013124465942</v>
+        <v>16.47195816040039</v>
       </c>
       <c r="E50" t="n">
-        <v>-20.71802520751953</v>
+        <v>-11.70621967315674</v>
       </c>
       <c r="F50" t="n">
-        <v>-26.17952156066895</v>
+        <v>-27.66258811950684</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>39.35417938232422</v>
+        <v>28.45382499694824</v>
       </c>
       <c r="B51" t="n">
-        <v>40.75213623046875</v>
+        <v>37.51952362060547</v>
       </c>
       <c r="C51" t="n">
-        <v>9.097759246826172</v>
+        <v>5.336234092712402</v>
       </c>
       <c r="D51" t="n">
-        <v>12.46080493927002</v>
+        <v>13.72345638275146</v>
       </c>
       <c r="E51" t="n">
-        <v>-20.15096664428711</v>
+        <v>-10.73466873168945</v>
       </c>
       <c r="F51" t="n">
-        <v>-25.68461990356445</v>
+        <v>-19.69185829162598</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>42.86943435668945</v>
+        <v>27.4360294342041</v>
       </c>
       <c r="B52" t="n">
-        <v>39.29502105712891</v>
+        <v>39.14389801025391</v>
       </c>
       <c r="C52" t="n">
-        <v>8.985234260559082</v>
+        <v>3.79353404045105</v>
       </c>
       <c r="D52" t="n">
-        <v>12.69133472442627</v>
+        <v>19.39817047119141</v>
       </c>
       <c r="E52" t="n">
-        <v>-14.29280376434326</v>
+        <v>-11.892409324646</v>
       </c>
       <c r="F52" t="n">
-        <v>-20.66024208068848</v>
+        <v>-19.52992248535156</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>41.08701705932617</v>
+        <v>27.80468940734863</v>
       </c>
       <c r="B53" t="n">
-        <v>36.67310333251953</v>
+        <v>38.21996307373047</v>
       </c>
       <c r="C53" t="n">
-        <v>14.11865329742432</v>
+        <v>4.74809741973877</v>
       </c>
       <c r="D53" t="n">
-        <v>16.55709075927734</v>
+        <v>15.43920612335205</v>
       </c>
       <c r="E53" t="n">
-        <v>-16.87677574157715</v>
+        <v>-9.493097305297852</v>
       </c>
       <c r="F53" t="n">
-        <v>-24.39663314819336</v>
+        <v>-17.40576362609863</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>42.46843719482422</v>
+        <v>25.78323745727539</v>
       </c>
       <c r="B54" t="n">
-        <v>36.08785247802734</v>
+        <v>36.12693405151367</v>
       </c>
       <c r="C54" t="n">
-        <v>16.71998596191406</v>
+        <v>5.070511817932129</v>
       </c>
       <c r="D54" t="n">
-        <v>17.54851722717285</v>
+        <v>17.49312210083008</v>
       </c>
       <c r="E54" t="n">
-        <v>-18.00593566894531</v>
+        <v>-11.8475513458252</v>
       </c>
       <c r="F54" t="n">
-        <v>-24.51765060424805</v>
+        <v>-17.06118011474609</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>44.35635375976562</v>
+        <v>26.82697486877441</v>
       </c>
       <c r="B55" t="n">
-        <v>35.23190689086914</v>
+        <v>34.82057571411133</v>
       </c>
       <c r="C55" t="n">
-        <v>19.26667022705078</v>
+        <v>5.406918525695801</v>
       </c>
       <c r="D55" t="n">
-        <v>19.53730773925781</v>
+        <v>17.43274307250977</v>
       </c>
       <c r="E55" t="n">
-        <v>-19.30146217346191</v>
+        <v>-12.32325744628906</v>
       </c>
       <c r="F55" t="n">
-        <v>-22.54453468322754</v>
+        <v>-16.89519882202148</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>43.1884651184082</v>
+        <v>26.70362091064453</v>
       </c>
       <c r="B56" t="n">
-        <v>33.90997695922852</v>
+        <v>35.1434326171875</v>
       </c>
       <c r="C56" t="n">
-        <v>20.3551197052002</v>
+        <v>2.957606077194214</v>
       </c>
       <c r="D56" t="n">
-        <v>21.29287147521973</v>
+        <v>18.60499000549316</v>
       </c>
       <c r="E56" t="n">
-        <v>-19.94792556762695</v>
+        <v>-11.6145601272583</v>
       </c>
       <c r="F56" t="n">
-        <v>-19.57552528381348</v>
+        <v>-16.34105491638184</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>42.24124526977539</v>
+        <v>27.37265396118164</v>
       </c>
       <c r="B57" t="n">
-        <v>29.66486167907715</v>
+        <v>34.81997299194336</v>
       </c>
       <c r="C57" t="n">
-        <v>22.90723609924316</v>
+        <v>3.975699186325073</v>
       </c>
       <c r="D57" t="n">
-        <v>20.24846076965332</v>
+        <v>19.77705764770508</v>
       </c>
       <c r="E57" t="n">
-        <v>-17.39941024780273</v>
+        <v>-13.50088691711426</v>
       </c>
       <c r="F57" t="n">
-        <v>-21.95207405090332</v>
+        <v>-15.67366886138916</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>40.42654418945312</v>
+        <v>26.65352821350098</v>
       </c>
       <c r="B58" t="n">
-        <v>28.84483528137207</v>
+        <v>35.58810424804688</v>
       </c>
       <c r="C58" t="n">
-        <v>25.44148635864258</v>
+        <v>3.474068403244019</v>
       </c>
       <c r="D58" t="n">
-        <v>21.39686584472656</v>
+        <v>19.68611526489258</v>
       </c>
       <c r="E58" t="n">
-        <v>-13.50195503234863</v>
+        <v>-13.28425598144531</v>
       </c>
       <c r="F58" t="n">
-        <v>-17.79773712158203</v>
+        <v>-12.43077945709229</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>38.96625518798828</v>
+        <v>24.39170455932617</v>
       </c>
       <c r="B59" t="n">
-        <v>27.18195533752441</v>
+        <v>33.97011184692383</v>
       </c>
       <c r="C59" t="n">
-        <v>22.65423965454102</v>
+        <v>2.786247968673706</v>
       </c>
       <c r="D59" t="n">
-        <v>22.20147705078125</v>
+        <v>19.93863296508789</v>
       </c>
       <c r="E59" t="n">
-        <v>-8.716479301452637</v>
+        <v>-12.04198265075684</v>
       </c>
       <c r="F59" t="n">
-        <v>-16.97858238220215</v>
+        <v>-9.996737480163574</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>36.05981826782227</v>
+        <v>25.16482925415039</v>
       </c>
       <c r="B60" t="n">
-        <v>27.23682403564453</v>
+        <v>30.6779956817627</v>
       </c>
       <c r="C60" t="n">
-        <v>22.34011268615723</v>
+        <v>3.655190229415894</v>
       </c>
       <c r="D60" t="n">
-        <v>20.80096244812012</v>
+        <v>17.99578475952148</v>
       </c>
       <c r="E60" t="n">
-        <v>-4.764694690704346</v>
+        <v>-12.23322868347168</v>
       </c>
       <c r="F60" t="n">
-        <v>-14.14727401733398</v>
+        <v>-9.635845184326172</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>33.34072875976562</v>
+        <v>24.09063339233398</v>
       </c>
       <c r="B61" t="n">
-        <v>26.18884468078613</v>
+        <v>29.20450019836426</v>
       </c>
       <c r="C61" t="n">
-        <v>22.52378082275391</v>
+        <v>4.056036949157715</v>
       </c>
       <c r="D61" t="n">
-        <v>19.97552680969238</v>
+        <v>16.65375900268555</v>
       </c>
       <c r="E61" t="n">
-        <v>-2.731288433074951</v>
+        <v>-10.4307861328125</v>
       </c>
       <c r="F61" t="n">
-        <v>-12.24511241912842</v>
+        <v>-4.918579578399658</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>30.67179679870605</v>
+        <v>24.30298805236816</v>
       </c>
       <c r="B62" t="n">
-        <v>24.35799217224121</v>
+        <v>27.93544960021973</v>
       </c>
       <c r="C62" t="n">
-        <v>20.90112495422363</v>
+        <v>4.307393074035645</v>
       </c>
       <c r="D62" t="n">
-        <v>20.87331199645996</v>
+        <v>17.83705520629883</v>
       </c>
       <c r="E62" t="n">
-        <v>-3.604633092880249</v>
+        <v>-9.271646499633789</v>
       </c>
       <c r="F62" t="n">
-        <v>-9.805938720703125</v>
+        <v>-3.000339508056641</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>28.62261390686035</v>
+        <v>22.89218711853027</v>
       </c>
       <c r="B63" t="n">
-        <v>22.50875473022461</v>
+        <v>27.4393138885498</v>
       </c>
       <c r="C63" t="n">
-        <v>19.40789222717285</v>
+        <v>3.41809344291687</v>
       </c>
       <c r="D63" t="n">
-        <v>19.60161590576172</v>
+        <v>16.47182273864746</v>
       </c>
       <c r="E63" t="n">
-        <v>-3.693544864654541</v>
+        <v>-8.422811508178711</v>
       </c>
       <c r="F63" t="n">
-        <v>-8.269742965698242</v>
+        <v>-2.232963800430298</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>27.0922966003418</v>
+        <v>21.57601547241211</v>
       </c>
       <c r="B64" t="n">
-        <v>21.72267723083496</v>
+        <v>25.19720268249512</v>
       </c>
       <c r="C64" t="n">
-        <v>19.84197235107422</v>
+        <v>3.379921674728394</v>
       </c>
       <c r="D64" t="n">
-        <v>20.00752067565918</v>
+        <v>15.53777122497559</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.7663893699646</v>
+        <v>-7.870267868041992</v>
       </c>
       <c r="F64" t="n">
-        <v>-5.758813858032227</v>
+        <v>-1.231777310371399</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>24.14131927490234</v>
+        <v>21.58468627929688</v>
       </c>
       <c r="B65" t="n">
-        <v>18.99734115600586</v>
+        <v>23.34868621826172</v>
       </c>
       <c r="C65" t="n">
-        <v>15.53333854675293</v>
+        <v>2.638951063156128</v>
       </c>
       <c r="D65" t="n">
-        <v>20.07223701477051</v>
+        <v>15.61417484283447</v>
       </c>
       <c r="E65" t="n">
-        <v>0.2294411659240723</v>
+        <v>-8.020805358886719</v>
       </c>
       <c r="F65" t="n">
-        <v>-4.627319812774658</v>
+        <v>0.8024210333824158</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>22.55522537231445</v>
+        <v>20.78667831420898</v>
       </c>
       <c r="B66" t="n">
-        <v>19.00732612609863</v>
+        <v>22.85670852661133</v>
       </c>
       <c r="C66" t="n">
-        <v>16.81167221069336</v>
+        <v>3.131743192672729</v>
       </c>
       <c r="D66" t="n">
-        <v>18.55153274536133</v>
+        <v>15.79967784881592</v>
       </c>
       <c r="E66" t="n">
-        <v>1.351276397705078</v>
+        <v>-8.249166488647461</v>
       </c>
       <c r="F66" t="n">
-        <v>-5.703691959381104</v>
+        <v>2.404088973999023</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>20.63813018798828</v>
+        <v>19.9261417388916</v>
       </c>
       <c r="B67" t="n">
-        <v>15.05264282226562</v>
+        <v>20.84084129333496</v>
       </c>
       <c r="C67" t="n">
-        <v>15.74210929870605</v>
+        <v>1.666546702384949</v>
       </c>
       <c r="D67" t="n">
-        <v>18.69441795349121</v>
+        <v>14.47272682189941</v>
       </c>
       <c r="E67" t="n">
-        <v>4.588352203369141</v>
+        <v>-8.625381469726562</v>
       </c>
       <c r="F67" t="n">
-        <v>-4.093141078948975</v>
+        <v>4.064601898193359</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>17.36743545532227</v>
+        <v>19.19337844848633</v>
       </c>
       <c r="B68" t="n">
-        <v>14.12564182281494</v>
+        <v>19.43781852722168</v>
       </c>
       <c r="C68" t="n">
-        <v>15.78021144866943</v>
+        <v>0.5049675107002258</v>
       </c>
       <c r="D68" t="n">
-        <v>16.98001289367676</v>
+        <v>14.26574611663818</v>
       </c>
       <c r="E68" t="n">
-        <v>5.456628799438477</v>
+        <v>-9.841204643249512</v>
       </c>
       <c r="F68" t="n">
-        <v>-4.089272499084473</v>
+        <v>3.853227615356445</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>14.39570140838623</v>
+        <v>18.01743316650391</v>
       </c>
       <c r="B69" t="n">
-        <v>10.97650241851807</v>
+        <v>17.7538948059082</v>
       </c>
       <c r="C69" t="n">
-        <v>12.90610885620117</v>
+        <v>0.8067291378974915</v>
       </c>
       <c r="D69" t="n">
-        <v>14.3260612487793</v>
+        <v>15.37849617004395</v>
       </c>
       <c r="E69" t="n">
-        <v>4.864131927490234</v>
+        <v>-9.961259841918945</v>
       </c>
       <c r="F69" t="n">
-        <v>-5.320446968078613</v>
+        <v>4.305944442749023</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>12.23880863189697</v>
+        <v>16.82940864562988</v>
       </c>
       <c r="B70" t="n">
-        <v>12.55375289916992</v>
+        <v>17.81906318664551</v>
       </c>
       <c r="C70" t="n">
-        <v>11.54572200775146</v>
+        <v>-0.3404819369316101</v>
       </c>
       <c r="D70" t="n">
-        <v>16.74458885192871</v>
+        <v>12.89828491210938</v>
       </c>
       <c r="E70" t="n">
-        <v>7.818572044372559</v>
+        <v>-10.66989517211914</v>
       </c>
       <c r="F70" t="n">
-        <v>-4.950210571289062</v>
+        <v>4.87744140625</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>11.27454471588135</v>
+        <v>13.38665771484375</v>
       </c>
       <c r="B71" t="n">
-        <v>8.952959060668945</v>
+        <v>14.31720733642578</v>
       </c>
       <c r="C71" t="n">
-        <v>13.63875007629395</v>
+        <v>-0.3508636355400085</v>
       </c>
       <c r="D71" t="n">
-        <v>16.4870719909668</v>
+        <v>13.45076751708984</v>
       </c>
       <c r="E71" t="n">
-        <v>7.720866203308105</v>
+        <v>-9.005659103393555</v>
       </c>
       <c r="F71" t="n">
-        <v>-4.761229515075684</v>
+        <v>5.808908462524414</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>7.748135089874268</v>
+        <v>14.22956562042236</v>
       </c>
       <c r="B72" t="n">
-        <v>7.770039558410645</v>
+        <v>14.24795532226562</v>
       </c>
       <c r="C72" t="n">
-        <v>12.1429500579834</v>
+        <v>-0.8861858248710632</v>
       </c>
       <c r="D72" t="n">
-        <v>15.12662124633789</v>
+        <v>14.26838397979736</v>
       </c>
       <c r="E72" t="n">
-        <v>11.24480533599854</v>
+        <v>-9.221213340759277</v>
       </c>
       <c r="F72" t="n">
-        <v>-3.490744590759277</v>
+        <v>5.721658706665039</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>9.889430999755859</v>
+        <v>11.73603820800781</v>
       </c>
       <c r="B73" t="n">
-        <v>7.099860191345215</v>
+        <v>14.02225303649902</v>
       </c>
       <c r="C73" t="n">
-        <v>14.09367942810059</v>
+        <v>4.460301399230957</v>
       </c>
       <c r="D73" t="n">
-        <v>18.97085952758789</v>
+        <v>13.97252750396729</v>
       </c>
       <c r="E73" t="n">
-        <v>9.033486366271973</v>
+        <v>-7.73922061920166</v>
       </c>
       <c r="F73" t="n">
-        <v>-6.212469100952148</v>
+        <v>5.849939346313477</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>8.017987251281738</v>
+        <v>10.50203037261963</v>
       </c>
       <c r="B74" t="n">
-        <v>5.373824119567871</v>
+        <v>12.27095985412598</v>
       </c>
       <c r="C74" t="n">
-        <v>14.85807418823242</v>
+        <v>5.111515998840332</v>
       </c>
       <c r="D74" t="n">
-        <v>18.76457405090332</v>
+        <v>14.93980979919434</v>
       </c>
       <c r="E74" t="n">
-        <v>10.10652446746826</v>
+        <v>-9.735326766967773</v>
       </c>
       <c r="F74" t="n">
-        <v>-6.077148914337158</v>
+        <v>6.531290054321289</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>5.920189380645752</v>
+        <v>9.571197509765625</v>
       </c>
       <c r="B75" t="n">
-        <v>4.674067497253418</v>
+        <v>10.43598937988281</v>
       </c>
       <c r="C75" t="n">
-        <v>15.80280685424805</v>
+        <v>6.187886238098145</v>
       </c>
       <c r="D75" t="n">
-        <v>20.30795288085938</v>
+        <v>16.11656761169434</v>
       </c>
       <c r="E75" t="n">
-        <v>8.177614212036133</v>
+        <v>-12.22723007202148</v>
       </c>
       <c r="F75" t="n">
-        <v>-8.279979705810547</v>
+        <v>2.252799034118652</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>5.135294437408447</v>
+        <v>8.412030220031738</v>
       </c>
       <c r="B76" t="n">
-        <v>8.974468231201172</v>
+        <v>12.22906970977783</v>
       </c>
       <c r="C76" t="n">
-        <v>17.0566291809082</v>
+        <v>6.738593101501465</v>
       </c>
       <c r="D76" t="n">
-        <v>23.29468154907227</v>
+        <v>15.60470199584961</v>
       </c>
       <c r="E76" t="n">
-        <v>3.71083927154541</v>
+        <v>-16.73851776123047</v>
       </c>
       <c r="F76" t="n">
-        <v>-11.0056324005127</v>
+        <v>0.908866822719574</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4.301228046417236</v>
+        <v>9.836722373962402</v>
       </c>
       <c r="B77" t="n">
-        <v>7.54233455657959</v>
+        <v>9.950628280639648</v>
       </c>
       <c r="C77" t="n">
-        <v>17.07280349731445</v>
+        <v>9.363038063049316</v>
       </c>
       <c r="D77" t="n">
-        <v>26.17250823974609</v>
+        <v>18.16049385070801</v>
       </c>
       <c r="E77" t="n">
-        <v>-3.489358425140381</v>
+        <v>-19.6083812713623</v>
       </c>
       <c r="F77" t="n">
-        <v>-20.08888244628906</v>
+        <v>-2.89827823638916</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>5.725063800811768</v>
+        <v>7.90493631362915</v>
       </c>
       <c r="B78" t="n">
-        <v>7.821490287780762</v>
+        <v>11.12720203399658</v>
       </c>
       <c r="C78" t="n">
-        <v>20.83128929138184</v>
+        <v>11.19491291046143</v>
       </c>
       <c r="D78" t="n">
-        <v>29.07435989379883</v>
+        <v>20.00704765319824</v>
       </c>
       <c r="E78" t="n">
-        <v>-11.52489566802979</v>
+        <v>-21.24637413024902</v>
       </c>
       <c r="F78" t="n">
-        <v>-25.83094024658203</v>
+        <v>-10.66457366943359</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>5.786606311798096</v>
+        <v>8.273783683776855</v>
       </c>
       <c r="B79" t="n">
-        <v>10.0399112701416</v>
+        <v>10.10579013824463</v>
       </c>
       <c r="C79" t="n">
-        <v>26.1441535949707</v>
+        <v>14.04183006286621</v>
       </c>
       <c r="D79" t="n">
-        <v>33.60885238647461</v>
+        <v>22.82454490661621</v>
       </c>
       <c r="E79" t="n">
-        <v>-23.10959053039551</v>
+        <v>-24.44217300415039</v>
       </c>
       <c r="F79" t="n">
-        <v>-31.04047393798828</v>
+        <v>-18.27659797668457</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>7.826529026031494</v>
+        <v>7.558458805084229</v>
       </c>
       <c r="B80" t="n">
-        <v>11.2746000289917</v>
+        <v>10.02665615081787</v>
       </c>
       <c r="C80" t="n">
-        <v>30.53293991088867</v>
+        <v>18.05062866210938</v>
       </c>
       <c r="D80" t="n">
-        <v>36.23822021484375</v>
+        <v>25.60901641845703</v>
       </c>
       <c r="E80" t="n">
-        <v>-33.47980117797852</v>
+        <v>-27.23437118530273</v>
       </c>
       <c r="F80" t="n">
-        <v>-39.67597198486328</v>
+        <v>-28.90147399902344</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>11.97700500488281</v>
+        <v>10.30841541290283</v>
       </c>
       <c r="B81" t="n">
-        <v>13.14146709442139</v>
+        <v>10.41455936431885</v>
       </c>
       <c r="C81" t="n">
-        <v>34.74702835083008</v>
+        <v>21.82324600219727</v>
       </c>
       <c r="D81" t="n">
-        <v>43.18555068969727</v>
+        <v>30.50455665588379</v>
       </c>
       <c r="E81" t="n">
-        <v>-42.95692825317383</v>
+        <v>-30.8314037322998</v>
       </c>
       <c r="F81" t="n">
-        <v>-46.9415283203125</v>
+        <v>-37.04381561279297</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>13.83821868896484</v>
+        <v>11.05416965484619</v>
       </c>
       <c r="B82" t="n">
-        <v>16.6893196105957</v>
+        <v>12.14208984375</v>
       </c>
       <c r="C82" t="n">
-        <v>39.29053497314453</v>
+        <v>26.78364753723145</v>
       </c>
       <c r="D82" t="n">
-        <v>46.94204330444336</v>
+        <v>34.89394760131836</v>
       </c>
       <c r="E82" t="n">
-        <v>-43.92324447631836</v>
+        <v>-32.3284912109375</v>
       </c>
       <c r="F82" t="n">
-        <v>-56.18206405639648</v>
+        <v>-47.85490036010742</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>17.76088714599609</v>
+        <v>14.17419052124023</v>
       </c>
       <c r="B83" t="n">
-        <v>17.75683403015137</v>
+        <v>13.6109561920166</v>
       </c>
       <c r="C83" t="n">
-        <v>47.09109497070312</v>
+        <v>32.48613739013672</v>
       </c>
       <c r="D83" t="n">
-        <v>49.85519790649414</v>
+        <v>39.29831695556641</v>
       </c>
       <c r="E83" t="n">
-        <v>-46.44026947021484</v>
+        <v>-33.66483688354492</v>
       </c>
       <c r="F83" t="n">
-        <v>-56.85717010498047</v>
+        <v>-53.73588943481445</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>19.94689178466797</v>
+        <v>16.35373497009277</v>
       </c>
       <c r="B84" t="n">
-        <v>23.18157958984375</v>
+        <v>16.33076667785645</v>
       </c>
       <c r="C84" t="n">
-        <v>50.52193832397461</v>
+        <v>34.83502197265625</v>
       </c>
       <c r="D84" t="n">
-        <v>52.85485076904297</v>
+        <v>43.85599899291992</v>
       </c>
       <c r="E84" t="n">
-        <v>-46.04673004150391</v>
+        <v>-35.81654739379883</v>
       </c>
       <c r="F84" t="n">
-        <v>-57.52158737182617</v>
+        <v>-55.37004470825195</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>24.47520637512207</v>
+        <v>18.88271141052246</v>
       </c>
       <c r="B85" t="n">
-        <v>24.4857063293457</v>
+        <v>19.14658355712891</v>
       </c>
       <c r="C85" t="n">
-        <v>52.06187438964844</v>
+        <v>39.76166915893555</v>
       </c>
       <c r="D85" t="n">
-        <v>55.7276496887207</v>
+        <v>47.89885711669922</v>
       </c>
       <c r="E85" t="n">
-        <v>-42.20121383666992</v>
+        <v>-36.54694747924805</v>
       </c>
       <c r="F85" t="n">
-        <v>-55.6297721862793</v>
+        <v>-58.01923370361328</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>26.92143821716309</v>
+        <v>22.21427917480469</v>
       </c>
       <c r="B86" t="n">
-        <v>28.59725379943848</v>
+        <v>22.1550350189209</v>
       </c>
       <c r="C86" t="n">
-        <v>55.52443695068359</v>
+        <v>43.75979614257812</v>
       </c>
       <c r="D86" t="n">
-        <v>58.08452606201172</v>
+        <v>49.95057678222656</v>
       </c>
       <c r="E86" t="n">
-        <v>-40.05070877075195</v>
+        <v>-32.77588272094727</v>
       </c>
       <c r="F86" t="n">
-        <v>-45.92124938964844</v>
+        <v>-56.54882431030273</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>29.28231620788574</v>
+        <v>25.07912445068359</v>
       </c>
       <c r="B87" t="n">
-        <v>31.21104431152344</v>
+        <v>25.56700134277344</v>
       </c>
       <c r="C87" t="n">
-        <v>56.28141403198242</v>
+        <v>43.99177932739258</v>
       </c>
       <c r="D87" t="n">
-        <v>57.26727294921875</v>
+        <v>54.33987426757812</v>
       </c>
       <c r="E87" t="n">
-        <v>-33.94269943237305</v>
+        <v>-31.84420967102051</v>
       </c>
       <c r="F87" t="n">
-        <v>-40.81689453125</v>
+        <v>-49.87140655517578</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>32.15611267089844</v>
+        <v>28.32108879089355</v>
       </c>
       <c r="B88" t="n">
-        <v>32.84739685058594</v>
+        <v>28.57834053039551</v>
       </c>
       <c r="C88" t="n">
-        <v>49.59470748901367</v>
+        <v>47.01157760620117</v>
       </c>
       <c r="D88" t="n">
-        <v>56.58465576171875</v>
+        <v>55.22407531738281</v>
       </c>
       <c r="E88" t="n">
-        <v>-28.37485694885254</v>
+        <v>-27.45145034790039</v>
       </c>
       <c r="F88" t="n">
-        <v>-35.39773178100586</v>
+        <v>-43.56353378295898</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>35.49474334716797</v>
+        <v>29.58629608154297</v>
       </c>
       <c r="B89" t="n">
-        <v>35.96508026123047</v>
+        <v>31.2404613494873</v>
       </c>
       <c r="C89" t="n">
-        <v>48.09792327880859</v>
+        <v>46.77302551269531</v>
       </c>
       <c r="D89" t="n">
-        <v>55.24594879150391</v>
+        <v>55.86564254760742</v>
       </c>
       <c r="E89" t="n">
-        <v>-24.89361763000488</v>
+        <v>-22.85531425476074</v>
       </c>
       <c r="F89" t="n">
-        <v>-31.75154495239258</v>
+        <v>-37.11527633666992</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>36.73117065429688</v>
+        <v>32.81131744384766</v>
       </c>
       <c r="B90" t="n">
-        <v>37.17492294311523</v>
+        <v>34.29693603515625</v>
       </c>
       <c r="C90" t="n">
-        <v>41.85103988647461</v>
+        <v>44.94423675537109</v>
       </c>
       <c r="D90" t="n">
-        <v>50.29325866699219</v>
+        <v>55.74142456054688</v>
       </c>
       <c r="E90" t="n">
-        <v>-21.10405731201172</v>
+        <v>-20.06022453308105</v>
       </c>
       <c r="F90" t="n">
-        <v>-29.11430931091309</v>
+        <v>-31.34889030456543</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>37.61338043212891</v>
+        <v>34.24991607666016</v>
       </c>
       <c r="B91" t="n">
-        <v>38.11126708984375</v>
+        <v>35.81399917602539</v>
       </c>
       <c r="C91" t="n">
-        <v>42.15758895874023</v>
+        <v>40.51909637451172</v>
       </c>
       <c r="D91" t="n">
-        <v>47.40512847900391</v>
+        <v>53.5333137512207</v>
       </c>
       <c r="E91" t="n">
-        <v>-19.45423889160156</v>
+        <v>-15.97498512268066</v>
       </c>
       <c r="F91" t="n">
-        <v>-24.67838668823242</v>
+        <v>-25.16924667358398</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>37.05133056640625</v>
+        <v>37.35476303100586</v>
       </c>
       <c r="B92" t="n">
-        <v>38.96053695678711</v>
+        <v>37.60959243774414</v>
       </c>
       <c r="C92" t="n">
-        <v>36.56715393066406</v>
+        <v>38.9886360168457</v>
       </c>
       <c r="D92" t="n">
-        <v>42.60195541381836</v>
+        <v>50.91184997558594</v>
       </c>
       <c r="E92" t="n">
-        <v>-17.54323387145996</v>
+        <v>-12.61406517028809</v>
       </c>
       <c r="F92" t="n">
-        <v>-25.20034027099609</v>
+        <v>-23.83709526062012</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>36.60656356811523</v>
+        <v>37.91129302978516</v>
       </c>
       <c r="B93" t="n">
-        <v>41.66750717163086</v>
+        <v>39.46142959594727</v>
       </c>
       <c r="C93" t="n">
-        <v>28.97946929931641</v>
+        <v>36.1848030090332</v>
       </c>
       <c r="D93" t="n">
-        <v>33.13285446166992</v>
+        <v>45.37398147583008</v>
       </c>
       <c r="E93" t="n">
-        <v>-15.66441345214844</v>
+        <v>-8.778200149536133</v>
       </c>
       <c r="F93" t="n">
-        <v>-22.81289100646973</v>
+        <v>-19.8355884552002</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>36.13813018798828</v>
+        <v>40.69366455078125</v>
       </c>
       <c r="B94" t="n">
-        <v>38.50467300415039</v>
+        <v>41.22139358520508</v>
       </c>
       <c r="C94" t="n">
-        <v>21.57572174072266</v>
+        <v>33.23648452758789</v>
       </c>
       <c r="D94" t="n">
-        <v>30.06538772583008</v>
+        <v>43.17547988891602</v>
       </c>
       <c r="E94" t="n">
-        <v>-14.40097713470459</v>
+        <v>-6.636445999145508</v>
       </c>
       <c r="F94" t="n">
-        <v>-21.64724159240723</v>
+        <v>-18.54378509521484</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>38.5946159362793</v>
+        <v>41.25310897827148</v>
       </c>
       <c r="B95" t="n">
-        <v>38.60725784301758</v>
+        <v>42.04779052734375</v>
       </c>
       <c r="C95" t="n">
-        <v>18.81217956542969</v>
+        <v>27.58132362365723</v>
       </c>
       <c r="D95" t="n">
-        <v>24.57038497924805</v>
+        <v>36.90519332885742</v>
       </c>
       <c r="E95" t="n">
-        <v>-9.156842231750488</v>
+        <v>-4.62289571762085</v>
       </c>
       <c r="F95" t="n">
-        <v>-23.89208602905273</v>
+        <v>-16.95985984802246</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>37.33149337768555</v>
+        <v>41.50802993774414</v>
       </c>
       <c r="B96" t="n">
-        <v>38.43960952758789</v>
+        <v>42.51284027099609</v>
       </c>
       <c r="C96" t="n">
-        <v>16.3977165222168</v>
+        <v>25.23111343383789</v>
       </c>
       <c r="D96" t="n">
-        <v>17.86234474182129</v>
+        <v>31.82303619384766</v>
       </c>
       <c r="E96" t="n">
-        <v>-9.094270706176758</v>
+        <v>-1.712099075317383</v>
       </c>
       <c r="F96" t="n">
-        <v>-21.31942939758301</v>
+        <v>-15.07995510101318</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>37.88380813598633</v>
+        <v>42.44857025146484</v>
       </c>
       <c r="B97" t="n">
-        <v>40.36091995239258</v>
+        <v>42.52758026123047</v>
       </c>
       <c r="C97" t="n">
-        <v>14.66257762908936</v>
+        <v>20.21274375915527</v>
       </c>
       <c r="D97" t="n">
-        <v>14.63195896148682</v>
+        <v>27.39509963989258</v>
       </c>
       <c r="E97" t="n">
-        <v>-8.949199676513672</v>
+        <v>-2.017660617828369</v>
       </c>
       <c r="F97" t="n">
-        <v>-21.46636199951172</v>
+        <v>-14.57752990722656</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>39.13798141479492</v>
+        <v>43.51318359375</v>
       </c>
       <c r="B98" t="n">
-        <v>39.09380722045898</v>
+        <v>44.00776290893555</v>
       </c>
       <c r="C98" t="n">
-        <v>13.14858055114746</v>
+        <v>17.34800720214844</v>
       </c>
       <c r="D98" t="n">
-        <v>11.7432165145874</v>
+        <v>23.39641952514648</v>
       </c>
       <c r="E98" t="n">
-        <v>-9.088705062866211</v>
+        <v>-0.6900134086608887</v>
       </c>
       <c r="F98" t="n">
-        <v>-21.77778053283691</v>
+        <v>-12.75115966796875</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>39.00410079956055</v>
+        <v>43.62889862060547</v>
       </c>
       <c r="B99" t="n">
-        <v>38.90819549560547</v>
+        <v>44.41923522949219</v>
       </c>
       <c r="C99" t="n">
-        <v>14.07211494445801</v>
+        <v>14.72912979125977</v>
       </c>
       <c r="D99" t="n">
-        <v>10.29056739807129</v>
+        <v>20.40858840942383</v>
       </c>
       <c r="E99" t="n">
-        <v>-12.3747091293335</v>
+        <v>-1.161709785461426</v>
       </c>
       <c r="F99" t="n">
-        <v>-20.23560333251953</v>
+        <v>-15.02913665771484</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>36.99061584472656</v>
+        <v>32.17837142944336</v>
       </c>
       <c r="B100" t="n">
-        <v>36.57624053955078</v>
+        <v>43.74583053588867</v>
       </c>
       <c r="C100" t="n">
-        <v>12.80213260650635</v>
+        <v>8.457894325256348</v>
       </c>
       <c r="D100" t="n">
-        <v>10.58812522888184</v>
+        <v>16.50580596923828</v>
       </c>
       <c r="E100" t="n">
-        <v>-12.71338272094727</v>
+        <v>-3.391513586044312</v>
       </c>
       <c r="F100" t="n">
-        <v>-22.22743225097656</v>
+        <v>-14.51576519012451</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>38.60993576049805</v>
+        <v>31.54116249084473</v>
       </c>
       <c r="B101" t="n">
-        <v>38.92876434326172</v>
+        <v>43.66518402099609</v>
       </c>
       <c r="C101" t="n">
-        <v>13.77876853942871</v>
+        <v>5.749091148376465</v>
       </c>
       <c r="D101" t="n">
-        <v>9.493426322937012</v>
+        <v>14.38982105255127</v>
       </c>
       <c r="E101" t="n">
-        <v>-15.1959981918335</v>
+        <v>-5.047815799713135</v>
       </c>
       <c r="F101" t="n">
-        <v>-23.5316276550293</v>
+        <v>-15.39843940734863</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>38.27039337158203</v>
+        <v>30.99647521972656</v>
       </c>
       <c r="B102" t="n">
-        <v>39.82552337646484</v>
+        <v>41.01795196533203</v>
       </c>
       <c r="C102" t="n">
-        <v>14.70625114440918</v>
+        <v>5.672125816345215</v>
       </c>
       <c r="D102" t="n">
-        <v>12.42749977111816</v>
+        <v>14.34191036224365</v>
       </c>
       <c r="E102" t="n">
-        <v>-14.72869110107422</v>
+        <v>-6.540231704711914</v>
       </c>
       <c r="F102" t="n">
-        <v>-24.37942886352539</v>
+        <v>-16.94339942932129</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>40.48039245605469</v>
+        <v>30.03456878662109</v>
       </c>
       <c r="B103" t="n">
-        <v>37.15269088745117</v>
+        <v>40.03165054321289</v>
       </c>
       <c r="C103" t="n">
-        <v>12.88510131835938</v>
+        <v>5.701725959777832</v>
       </c>
       <c r="D103" t="n">
-        <v>14.24432277679443</v>
+        <v>14.12054538726807</v>
       </c>
       <c r="E103" t="n">
-        <v>-13.64500045776367</v>
+        <v>-9.267820358276367</v>
       </c>
       <c r="F103" t="n">
-        <v>-25.5816822052002</v>
+        <v>-17.26802825927734</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>41.29883193969727</v>
+        <v>27.38364791870117</v>
       </c>
       <c r="B104" t="n">
-        <v>36.68533325195312</v>
+        <v>38.58383941650391</v>
       </c>
       <c r="C104" t="n">
-        <v>17.5239372253418</v>
+        <v>4.572421073913574</v>
       </c>
       <c r="D104" t="n">
-        <v>17.80343437194824</v>
+        <v>15.1993293762207</v>
       </c>
       <c r="E104" t="n">
-        <v>-17.89146423339844</v>
+        <v>-9.385015487670898</v>
       </c>
       <c r="F104" t="n">
-        <v>-25.14709854125977</v>
+        <v>-16.79251480102539</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>41.81009292602539</v>
+        <v>25.78490447998047</v>
       </c>
       <c r="B105" t="n">
-        <v>35.32678604125977</v>
+        <v>36.55873870849609</v>
       </c>
       <c r="C105" t="n">
-        <v>19.25307464599609</v>
+        <v>4.781411170959473</v>
       </c>
       <c r="D105" t="n">
-        <v>18.82895469665527</v>
+        <v>17.13697814941406</v>
       </c>
       <c r="E105" t="n">
-        <v>-19.32416915893555</v>
+        <v>-11.50023365020752</v>
       </c>
       <c r="F105" t="n">
-        <v>-24.85800743103027</v>
+        <v>-16.68765258789062</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>42.98538970947266</v>
+        <v>25.63185882568359</v>
       </c>
       <c r="B106" t="n">
-        <v>35.12946701049805</v>
+        <v>35.52093124389648</v>
       </c>
       <c r="C106" t="n">
-        <v>22.08709144592285</v>
+        <v>4.469630241394043</v>
       </c>
       <c r="D106" t="n">
-        <v>21.48810195922852</v>
+        <v>17.2224292755127</v>
       </c>
       <c r="E106" t="n">
-        <v>-19.56134033203125</v>
+        <v>-12.11297607421875</v>
       </c>
       <c r="F106" t="n">
-        <v>-22.59672927856445</v>
+        <v>-16.53489685058594</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>42.59553909301758</v>
+        <v>25.62720108032227</v>
       </c>
       <c r="B107" t="n">
-        <v>33.65523910522461</v>
+        <v>35.73518753051758</v>
       </c>
       <c r="C107" t="n">
-        <v>23.8290843963623</v>
+        <v>2.676945447921753</v>
       </c>
       <c r="D107" t="n">
-        <v>23.21053123474121</v>
+        <v>18.73260116577148</v>
       </c>
       <c r="E107" t="n">
-        <v>-18.44443511962891</v>
+        <v>-11.72734928131104</v>
       </c>
       <c r="F107" t="n">
-        <v>-20.14111328125</v>
+        <v>-16.05660247802734</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>41.95796966552734</v>
+        <v>26.8554630279541</v>
       </c>
       <c r="B108" t="n">
-        <v>31.31833457946777</v>
+        <v>35.26398849487305</v>
       </c>
       <c r="C108" t="n">
-        <v>26.07048988342285</v>
+        <v>4.294682502746582</v>
       </c>
       <c r="D108" t="n">
-        <v>22.54880142211914</v>
+        <v>20.15327072143555</v>
       </c>
       <c r="E108" t="n">
-        <v>-15.63664245605469</v>
+        <v>-13.27190589904785</v>
       </c>
       <c r="F108" t="n">
-        <v>-21.06937980651855</v>
+        <v>-15.14661312103271</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>40.20413970947266</v>
+        <v>26.00690269470215</v>
       </c>
       <c r="B109" t="n">
-        <v>30.13427734375</v>
+        <v>35.94429779052734</v>
       </c>
       <c r="C109" t="n">
-        <v>27.67612838745117</v>
+        <v>3.972748517990112</v>
       </c>
       <c r="D109" t="n">
-        <v>23.17887115478516</v>
+        <v>20.41508865356445</v>
       </c>
       <c r="E109" t="n">
-        <v>-11.84837341308594</v>
+        <v>-12.65218257904053</v>
       </c>
       <c r="F109" t="n">
-        <v>-16.86820793151855</v>
+        <v>-12.03261184692383</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>38.32747268676758</v>
+        <v>24.1361141204834</v>
       </c>
       <c r="B110" t="n">
-        <v>28.79137802124023</v>
+        <v>33.83199691772461</v>
       </c>
       <c r="C110" t="n">
-        <v>25.43968391418457</v>
+        <v>3.887959241867065</v>
       </c>
       <c r="D110" t="n">
-        <v>23.28902626037598</v>
+        <v>20.64934349060059</v>
       </c>
       <c r="E110" t="n">
-        <v>-7.325994968414307</v>
+        <v>-11.67924499511719</v>
       </c>
       <c r="F110" t="n">
-        <v>-15.77417755126953</v>
+        <v>-9.348508834838867</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>35.95932006835938</v>
+        <v>24.47915267944336</v>
       </c>
       <c r="B111" t="n">
-        <v>26.93911743164062</v>
+        <v>30.99616432189941</v>
       </c>
       <c r="C111" t="n">
-        <v>24.98458290100098</v>
+        <v>4.307169914245605</v>
       </c>
       <c r="D111" t="n">
-        <v>22.48053359985352</v>
+        <v>18.99863815307617</v>
       </c>
       <c r="E111" t="n">
-        <v>-4.701449871063232</v>
+        <v>-11.23332977294922</v>
       </c>
       <c r="F111" t="n">
-        <v>-12.88658046722412</v>
+        <v>-8.821125984191895</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>33.4682502746582</v>
+        <v>23.63677787780762</v>
       </c>
       <c r="B112" t="n">
-        <v>26.21133613586426</v>
+        <v>29.53915405273438</v>
       </c>
       <c r="C112" t="n">
-        <v>24.12751579284668</v>
+        <v>4.548369407653809</v>
       </c>
       <c r="D112" t="n">
-        <v>21.12093544006348</v>
+        <v>17.81221580505371</v>
       </c>
       <c r="E112" t="n">
-        <v>-3.297863960266113</v>
+        <v>-10.21401214599609</v>
       </c>
       <c r="F112" t="n">
-        <v>-11.83360195159912</v>
+        <v>-4.05272102355957</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>30.46193313598633</v>
+        <v>23.11996841430664</v>
       </c>
       <c r="B113" t="n">
-        <v>24.23771095275879</v>
+        <v>28.02219772338867</v>
       </c>
       <c r="C113" t="n">
-        <v>22.4681224822998</v>
+        <v>4.712878227233887</v>
       </c>
       <c r="D113" t="n">
-        <v>21.41461181640625</v>
+        <v>18.78591537475586</v>
       </c>
       <c r="E113" t="n">
-        <v>-3.452521800994873</v>
+        <v>-8.530765533447266</v>
       </c>
       <c r="F113" t="n">
-        <v>-10.25658798217773</v>
+        <v>-2.032421112060547</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>28.77868461608887</v>
+        <v>21.6793384552002</v>
       </c>
       <c r="B114" t="n">
-        <v>21.77599143981934</v>
+        <v>27.6326847076416</v>
       </c>
       <c r="C114" t="n">
-        <v>21.22928810119629</v>
+        <v>4.314444541931152</v>
       </c>
       <c r="D114" t="n">
-        <v>19.56829071044922</v>
+        <v>17.91328811645508</v>
       </c>
       <c r="E114" t="n">
-        <v>-3.299551486968994</v>
+        <v>-7.816989421844482</v>
       </c>
       <c r="F114" t="n">
-        <v>-9.14926815032959</v>
+        <v>-1.777840256690979</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>26.51303100585938</v>
+        <v>20.70657157897949</v>
       </c>
       <c r="B115" t="n">
-        <v>20.5394344329834</v>
+        <v>25.09907722473145</v>
       </c>
       <c r="C115" t="n">
-        <v>20.21925735473633</v>
+        <v>4.347270011901855</v>
       </c>
       <c r="D115" t="n">
-        <v>18.66180229187012</v>
+        <v>16.33625030517578</v>
       </c>
       <c r="E115" t="n">
-        <v>-2.350761890411377</v>
+        <v>-6.791537284851074</v>
       </c>
       <c r="F115" t="n">
-        <v>-7.342602729797363</v>
+        <v>-0.4937453866004944</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>23.86797523498535</v>
+        <v>20.51431083679199</v>
       </c>
       <c r="B116" t="n">
-        <v>18.60179328918457</v>
+        <v>23.43719100952148</v>
       </c>
       <c r="C116" t="n">
-        <v>17.16361808776855</v>
+        <v>3.640480756759644</v>
       </c>
       <c r="D116" t="n">
-        <v>18.16649627685547</v>
+        <v>16.34069633483887</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.94207763671875</v>
+        <v>-6.266205787658691</v>
       </c>
       <c r="F116" t="n">
-        <v>-7.067862033843994</v>
+        <v>1.059760928153992</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>22.0541877746582</v>
+        <v>19.56692314147949</v>
       </c>
       <c r="B117" t="n">
-        <v>17.38972473144531</v>
+        <v>22.39385032653809</v>
       </c>
       <c r="C117" t="n">
-        <v>16.87517547607422</v>
+        <v>4.791388511657715</v>
       </c>
       <c r="D117" t="n">
-        <v>16.53684043884277</v>
+        <v>16.47250747680664</v>
       </c>
       <c r="E117" t="n">
-        <v>0.05887366086244583</v>
+        <v>-6.647429466247559</v>
       </c>
       <c r="F117" t="n">
-        <v>-7.823997497558594</v>
+        <v>2.375658988952637</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>20.19932174682617</v>
+        <v>18.71449279785156</v>
       </c>
       <c r="B118" t="n">
-        <v>14.21876430511475</v>
+        <v>20.85822486877441</v>
       </c>
       <c r="C118" t="n">
-        <v>16.3155632019043</v>
+        <v>2.910374402999878</v>
       </c>
       <c r="D118" t="n">
-        <v>16.02807998657227</v>
+        <v>14.42189979553223</v>
       </c>
       <c r="E118" t="n">
-        <v>2.356034278869629</v>
+        <v>-6.663987636566162</v>
       </c>
       <c r="F118" t="n">
-        <v>-6.314780712127686</v>
+        <v>3.573084831237793</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>17.34122657775879</v>
+        <v>18.11704063415527</v>
       </c>
       <c r="B119" t="n">
-        <v>13.13862228393555</v>
+        <v>19.20056533813477</v>
       </c>
       <c r="C119" t="n">
-        <v>15.2072811126709</v>
+        <v>2.033344984054565</v>
       </c>
       <c r="D119" t="n">
-        <v>14.78748035430908</v>
+        <v>14.06897354125977</v>
       </c>
       <c r="E119" t="n">
-        <v>2.889276504516602</v>
+        <v>-7.528524875640869</v>
       </c>
       <c r="F119" t="n">
-        <v>-7.047140121459961</v>
+        <v>3.094314575195312</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>14.64969062805176</v>
+        <v>16.7713737487793</v>
       </c>
       <c r="B120" t="n">
-        <v>10.08289051055908</v>
+        <v>17.84364700317383</v>
       </c>
       <c r="C120" t="n">
-        <v>13.85530281066895</v>
+        <v>2.544539213180542</v>
       </c>
       <c r="D120" t="n">
-        <v>12.37689208984375</v>
+        <v>15.27239513397217</v>
       </c>
       <c r="E120" t="n">
-        <v>3.517335891723633</v>
+        <v>-7.627467155456543</v>
       </c>
       <c r="F120" t="n">
-        <v>-7.363796710968018</v>
+        <v>3.139604568481445</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>12.41455078125</v>
+        <v>15.59827899932861</v>
       </c>
       <c r="B121" t="n">
-        <v>10.42111110687256</v>
+        <v>17.26610374450684</v>
       </c>
       <c r="C121" t="n">
-        <v>12.50212860107422</v>
+        <v>1.261000514030457</v>
       </c>
       <c r="D121" t="n">
-        <v>13.89250946044922</v>
+        <v>12.43497943878174</v>
       </c>
       <c r="E121" t="n">
-        <v>5.387526512145996</v>
+        <v>-8.218226432800293</v>
       </c>
       <c r="F121" t="n">
-        <v>-6.742639064788818</v>
+        <v>3.303162574768066</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>11.13689422607422</v>
+        <v>12.838547706604</v>
       </c>
       <c r="B122" t="n">
-        <v>7.375107765197754</v>
+        <v>13.90660762786865</v>
       </c>
       <c r="C122" t="n">
-        <v>13.48961067199707</v>
+        <v>1.183836817741394</v>
       </c>
       <c r="D122" t="n">
-        <v>13.22016429901123</v>
+        <v>12.73490047454834</v>
       </c>
       <c r="E122" t="n">
-        <v>5.405207633972168</v>
+        <v>-7.32444953918457</v>
       </c>
       <c r="F122" t="n">
-        <v>-6.945757865905762</v>
+        <v>3.716856002807617</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>8.51174259185791</v>
+        <v>13.48063468933105</v>
       </c>
       <c r="B123" t="n">
-        <v>6.399506568908691</v>
+        <v>14.0707540512085</v>
       </c>
       <c r="C123" t="n">
-        <v>12.50066375732422</v>
+        <v>0.9555023312568665</v>
       </c>
       <c r="D123" t="n">
-        <v>13.26010131835938</v>
+        <v>13.51815986633301</v>
       </c>
       <c r="E123" t="n">
-        <v>8.280576705932617</v>
+        <v>-7.940520286560059</v>
       </c>
       <c r="F123" t="n">
-        <v>-5.426542282104492</v>
+        <v>3.780067443847656</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>8.008858680725098</v>
+        <v>11.23554992675781</v>
       </c>
       <c r="B124" t="n">
-        <v>5.822367668151855</v>
+        <v>13.79934978485107</v>
       </c>
       <c r="C124" t="n">
-        <v>13.92518997192383</v>
+        <v>6.383139610290527</v>
       </c>
       <c r="D124" t="n">
-        <v>15.28836250305176</v>
+        <v>13.64959907531738</v>
       </c>
       <c r="E124" t="n">
-        <v>7.354777336120605</v>
+        <v>-6.516828060150146</v>
       </c>
       <c r="F124" t="n">
-        <v>-6.92603063583374</v>
+        <v>3.55463981628418</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>6.910427570343018</v>
+        <v>9.851189613342285</v>
       </c>
       <c r="B125" t="n">
-        <v>4.46878719329834</v>
+        <v>12.09092903137207</v>
       </c>
       <c r="C125" t="n">
-        <v>15.48777484893799</v>
+        <v>7.083931922912598</v>
       </c>
       <c r="D125" t="n">
-        <v>16.12955093383789</v>
+        <v>14.88765335083008</v>
       </c>
       <c r="E125" t="n">
-        <v>9.030133247375488</v>
+        <v>-8.718026161193848</v>
       </c>
       <c r="F125" t="n">
-        <v>-6.420915126800537</v>
+        <v>4.083944320678711</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>5.406691074371338</v>
+        <v>9.698666572570801</v>
       </c>
       <c r="B126" t="n">
-        <v>3.559826612472534</v>
+        <v>10.31341457366943</v>
       </c>
       <c r="C126" t="n">
-        <v>16.79750061035156</v>
+        <v>8.716977119445801</v>
       </c>
       <c r="D126" t="n">
-        <v>17.68133735656738</v>
+        <v>15.95086574554443</v>
       </c>
       <c r="E126" t="n">
-        <v>8.33107852935791</v>
+        <v>-11.51018810272217</v>
       </c>
       <c r="F126" t="n">
-        <v>-7.644883155822754</v>
+        <v>0.6823076605796814</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>4.774559497833252</v>
+        <v>9.178624153137207</v>
       </c>
       <c r="B127" t="n">
-        <v>5.671378135681152</v>
+        <v>11.93149948120117</v>
       </c>
       <c r="C127" t="n">
-        <v>18.66617774963379</v>
+        <v>9.499791145324707</v>
       </c>
       <c r="D127" t="n">
-        <v>20.60065841674805</v>
+        <v>15.89090919494629</v>
       </c>
       <c r="E127" t="n">
-        <v>4.985613822937012</v>
+        <v>-16.80237770080566</v>
       </c>
       <c r="F127" t="n">
-        <v>-10.08243465423584</v>
+        <v>-1.158650040626526</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>4.280788898468018</v>
+        <v>10.18192481994629</v>
       </c>
       <c r="B128" t="n">
-        <v>5.309525489807129</v>
+        <v>10.0540828704834</v>
       </c>
       <c r="C128" t="n">
-        <v>20.33122062683105</v>
+        <v>12.84450626373291</v>
       </c>
       <c r="D128" t="n">
-        <v>23.3477668762207</v>
+        <v>18.56049728393555</v>
       </c>
       <c r="E128" t="n">
-        <v>-1.615064144134521</v>
+        <v>-20.66426086425781</v>
       </c>
       <c r="F128" t="n">
-        <v>-17.05591011047363</v>
+        <v>-5.682810306549072</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>6.002760410308838</v>
+        <v>8.59776496887207</v>
       </c>
       <c r="B129" t="n">
-        <v>6.187411308288574</v>
+        <v>11.15826034545898</v>
       </c>
       <c r="C129" t="n">
-        <v>23.48921394348145</v>
+        <v>14.88020706176758</v>
       </c>
       <c r="D129" t="n">
-        <v>26.85177040100098</v>
+        <v>20.86752319335938</v>
       </c>
       <c r="E129" t="n">
-        <v>-10.14779472351074</v>
+        <v>-22.75129318237305</v>
       </c>
       <c r="F129" t="n">
-        <v>-24.28562927246094</v>
+        <v>-12.81411361694336</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>6.408335208892822</v>
+        <v>9.136996269226074</v>
       </c>
       <c r="B130" t="n">
-        <v>8.196484565734863</v>
+        <v>10.50304794311523</v>
       </c>
       <c r="C130" t="n">
-        <v>29.0233325958252</v>
+        <v>17.71358299255371</v>
       </c>
       <c r="D130" t="n">
-        <v>31.29620170593262</v>
+        <v>24.39598083496094</v>
       </c>
       <c r="E130" t="n">
-        <v>-22.63083839416504</v>
+        <v>-25.88484001159668</v>
       </c>
       <c r="F130" t="n">
-        <v>-31.26503372192383</v>
+        <v>-20.84426116943359</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>8.415478706359863</v>
+        <v>8.92147159576416</v>
       </c>
       <c r="B131" t="n">
-        <v>9.508636474609375</v>
+        <v>10.65510177612305</v>
       </c>
       <c r="C131" t="n">
-        <v>33.27346801757812</v>
+        <v>21.87299919128418</v>
       </c>
       <c r="D131" t="n">
-        <v>34.54758071899414</v>
+        <v>27.0738468170166</v>
       </c>
       <c r="E131" t="n">
-        <v>-33.99672698974609</v>
+        <v>-29.16891670227051</v>
       </c>
       <c r="F131" t="n">
-        <v>-41.36481094360352</v>
+        <v>-31.46716499328613</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>11.2415771484375</v>
+        <v>11.79825782775879</v>
       </c>
       <c r="B132" t="n">
-        <v>11.23580360412598</v>
+        <v>11.40180397033691</v>
       </c>
       <c r="C132" t="n">
-        <v>38.08513259887695</v>
+        <v>25.81787872314453</v>
       </c>
       <c r="D132" t="n">
-        <v>39.92307281494141</v>
+        <v>32.42975616455078</v>
       </c>
       <c r="E132" t="n">
-        <v>-44.25442123413086</v>
+        <v>-32.20015335083008</v>
       </c>
       <c r="F132" t="n">
-        <v>-49.93661880493164</v>
+        <v>-39.20508193969727</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>13.67661380767822</v>
+        <v>12.92533683776855</v>
       </c>
       <c r="B133" t="n">
-        <v>15.31201267242432</v>
+        <v>12.90273189544678</v>
       </c>
       <c r="C133" t="n">
-        <v>42.46918106079102</v>
+        <v>30.7630786895752</v>
       </c>
       <c r="D133" t="n">
-        <v>44.46809005737305</v>
+        <v>36.53359222412109</v>
       </c>
       <c r="E133" t="n">
-        <v>-47.57670211791992</v>
+        <v>-33.49620056152344</v>
       </c>
       <c r="F133" t="n">
-        <v>-57.17005920410156</v>
+        <v>-49.76542663574219</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>17.46278190612793</v>
+        <v>15.7176628112793</v>
       </c>
       <c r="B134" t="n">
-        <v>17.00683212280273</v>
+        <v>15.10895156860352</v>
       </c>
       <c r="C134" t="n">
-        <v>48.37408447265625</v>
+        <v>35.4803581237793</v>
       </c>
       <c r="D134" t="n">
-        <v>47.76923370361328</v>
+        <v>41.08961486816406</v>
       </c>
       <c r="E134" t="n">
-        <v>-48.35451889038086</v>
+        <v>-35.06210327148438</v>
       </c>
       <c r="F134" t="n">
-        <v>-57.25371932983398</v>
+        <v>-55.2000732421875</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>19.94636344909668</v>
+        <v>17.86311340332031</v>
       </c>
       <c r="B135" t="n">
-        <v>21.47469711303711</v>
+        <v>17.40135192871094</v>
       </c>
       <c r="C135" t="n">
-        <v>51.48760986328125</v>
+        <v>38.62608337402344</v>
       </c>
       <c r="D135" t="n">
-        <v>50.76388931274414</v>
+        <v>45.67325973510742</v>
       </c>
       <c r="E135" t="n">
-        <v>-46.61273956298828</v>
+        <v>-35.50007629394531</v>
       </c>
       <c r="F135" t="n">
-        <v>-56.18021011352539</v>
+        <v>-56.57267761230469</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>24.26774978637695</v>
+        <v>20.79289817810059</v>
       </c>
       <c r="B136" t="n">
-        <v>23.84159660339355</v>
+        <v>20.09135627746582</v>
       </c>
       <c r="C136" t="n">
-        <v>54.35093688964844</v>
+        <v>42.93019104003906</v>
       </c>
       <c r="D136" t="n">
-        <v>54.44200897216797</v>
+        <v>49.5084114074707</v>
       </c>
       <c r="E136" t="n">
-        <v>-41.36449813842773</v>
+        <v>-35.72987365722656</v>
       </c>
       <c r="F136" t="n">
-        <v>-51.02451705932617</v>
+        <v>-57.71936416625977</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>27.01223373413086</v>
+        <v>24.2525463104248</v>
       </c>
       <c r="B137" t="n">
-        <v>28.04544639587402</v>
+        <v>22.84110450744629</v>
       </c>
       <c r="C137" t="n">
-        <v>57.11809158325195</v>
+        <v>46.18406677246094</v>
       </c>
       <c r="D137" t="n">
-        <v>56.42412948608398</v>
+        <v>50.5658073425293</v>
       </c>
       <c r="E137" t="n">
-        <v>-36.42637634277344</v>
+        <v>-31.7086009979248</v>
       </c>
       <c r="F137" t="n">
-        <v>-42.63319778442383</v>
+        <v>-55.75336074829102</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>30.12612915039062</v>
+        <v>26.96737861633301</v>
       </c>
       <c r="B138" t="n">
-        <v>30.53005409240723</v>
+        <v>26.30647277832031</v>
       </c>
       <c r="C138" t="n">
-        <v>58.19232559204102</v>
+        <v>46.43480682373047</v>
       </c>
       <c r="D138" t="n">
-        <v>56.39157104492188</v>
+        <v>54.32938766479492</v>
       </c>
       <c r="E138" t="n">
-        <v>-30.80391693115234</v>
+        <v>-29.99601936340332</v>
       </c>
       <c r="F138" t="n">
-        <v>-37.31898498535156</v>
+        <v>-49.37831497192383</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>32.45485305786133</v>
+        <v>29.92212867736816</v>
       </c>
       <c r="B139" t="n">
-        <v>32.81507110595703</v>
+        <v>29.05441093444824</v>
       </c>
       <c r="C139" t="n">
-        <v>52.82281875610352</v>
+        <v>47.97954940795898</v>
       </c>
       <c r="D139" t="n">
-        <v>54.94239044189453</v>
+        <v>55.17932510375977</v>
       </c>
       <c r="E139" t="n">
-        <v>-26.52111625671387</v>
+        <v>-25.91753959655762</v>
       </c>
       <c r="F139" t="n">
-        <v>-32.58269500732422</v>
+        <v>-42.53973007202148</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>35.37313079833984</v>
+        <v>31.51178741455078</v>
       </c>
       <c r="B140" t="n">
-        <v>35.26916885375977</v>
+        <v>31.53548049926758</v>
       </c>
       <c r="C140" t="n">
-        <v>52.02969360351562</v>
+        <v>47.98833084106445</v>
       </c>
       <c r="D140" t="n">
-        <v>53.64593887329102</v>
+        <v>56.01968765258789</v>
       </c>
       <c r="E140" t="n">
-        <v>-23.66964340209961</v>
+        <v>-20.98870086669922</v>
       </c>
       <c r="F140" t="n">
-        <v>-28.80587196350098</v>
+        <v>-36.13236999511719</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>36.81250762939453</v>
+        <v>34.37299346923828</v>
       </c>
       <c r="B141" t="n">
-        <v>37.34701919555664</v>
+        <v>34.19133377075195</v>
       </c>
       <c r="C141" t="n">
-        <v>46.20336151123047</v>
+        <v>46.04273223876953</v>
       </c>
       <c r="D141" t="n">
-        <v>49.63605117797852</v>
+        <v>54.44316101074219</v>
       </c>
       <c r="E141" t="n">
-        <v>-20.60120391845703</v>
+        <v>-18.14991569519043</v>
       </c>
       <c r="F141" t="n">
-        <v>-26.63379287719727</v>
+        <v>-30.45640563964844</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>37.93122863769531</v>
+        <v>35.79751205444336</v>
       </c>
       <c r="B142" t="n">
-        <v>38.567626953125</v>
+        <v>36.07275390625</v>
       </c>
       <c r="C142" t="n">
-        <v>44.40044784545898</v>
+        <v>41.25463485717773</v>
       </c>
       <c r="D142" t="n">
-        <v>46.83806610107422</v>
+        <v>51.89646148681641</v>
       </c>
       <c r="E142" t="n">
-        <v>-18.65002632141113</v>
+        <v>-13.36004066467285</v>
       </c>
       <c r="F142" t="n">
-        <v>-23.4466495513916</v>
+        <v>-23.9709644317627</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>38.10063171386719</v>
+        <v>38.4312629699707</v>
       </c>
       <c r="B143" t="n">
-        <v>39.01554107666016</v>
+        <v>37.44940567016602</v>
       </c>
       <c r="C143" t="n">
-        <v>39.82873916625977</v>
+        <v>39.6345100402832</v>
       </c>
       <c r="D143" t="n">
-        <v>41.48275375366211</v>
+        <v>49.2213134765625</v>
       </c>
       <c r="E143" t="n">
-        <v>-16.42307662963867</v>
+        <v>-10.76401233673096</v>
       </c>
       <c r="F143" t="n">
-        <v>-23.49171829223633</v>
+        <v>-22.06108474731445</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>37.68827819824219</v>
+        <v>39.05604934692383</v>
       </c>
       <c r="B144" t="n">
-        <v>40.59146118164062</v>
+        <v>39.68891143798828</v>
       </c>
       <c r="C144" t="n">
-        <v>33.01410675048828</v>
+        <v>36.13188934326172</v>
       </c>
       <c r="D144" t="n">
-        <v>34.3752555847168</v>
+        <v>44.19469451904297</v>
       </c>
       <c r="E144" t="n">
-        <v>-14.71950721740723</v>
+        <v>-6.599008560180664</v>
       </c>
       <c r="F144" t="n">
-        <v>-20.99496269226074</v>
+        <v>-17.82277488708496</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>37.70835113525391</v>
+        <v>41.70668792724609</v>
       </c>
       <c r="B145" t="n">
-        <v>38.55446243286133</v>
+        <v>40.81105041503906</v>
       </c>
       <c r="C145" t="n">
-        <v>26.58610534667969</v>
+        <v>33.22290420532227</v>
       </c>
       <c r="D145" t="n">
-        <v>30.51550483703613</v>
+        <v>41.27465438842773</v>
       </c>
       <c r="E145" t="n">
-        <v>-12.82303714752197</v>
+        <v>-4.354237079620361</v>
       </c>
       <c r="F145" t="n">
-        <v>-20.42901420593262</v>
+        <v>-16.20771217346191</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>39.34318923950195</v>
+        <v>41.81689834594727</v>
       </c>
       <c r="B146" t="n">
-        <v>38.86461639404297</v>
+        <v>41.61049270629883</v>
       </c>
       <c r="C146" t="n">
-        <v>22.62310028076172</v>
+        <v>27.40004920959473</v>
       </c>
       <c r="D146" t="n">
-        <v>24.63751411437988</v>
+        <v>35.51791763305664</v>
       </c>
       <c r="E146" t="n">
-        <v>-9.513908386230469</v>
+        <v>-2.781158447265625</v>
       </c>
       <c r="F146" t="n">
-        <v>-21.50704956054688</v>
+        <v>-14.48948001861572</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>37.93248748779297</v>
+        <v>42.38268661499023</v>
       </c>
       <c r="B147" t="n">
-        <v>38.15436935424805</v>
+        <v>42.21273803710938</v>
       </c>
       <c r="C147" t="n">
-        <v>18.53798484802246</v>
+        <v>25.01833152770996</v>
       </c>
       <c r="D147" t="n">
-        <v>18.73050689697266</v>
+        <v>30.60148429870605</v>
       </c>
       <c r="E147" t="n">
-        <v>-8.549872398376465</v>
+        <v>-0.3172898292541504</v>
       </c>
       <c r="F147" t="n">
-        <v>-19.60045433044434</v>
+        <v>-12.3129940032959</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>38.24160766601562</v>
+        <v>41.53752517700195</v>
       </c>
       <c r="B148" t="n">
-        <v>38.63031768798828</v>
+        <v>42.22941589355469</v>
       </c>
       <c r="C148" t="n">
-        <v>16.79812049865723</v>
+        <v>19.84785652160645</v>
       </c>
       <c r="D148" t="n">
-        <v>14.87261009216309</v>
+        <v>25.93396759033203</v>
       </c>
       <c r="E148" t="n">
-        <v>-8.164876937866211</v>
+        <v>-0.1149883195757866</v>
       </c>
       <c r="F148" t="n">
-        <v>-19.29784393310547</v>
+        <v>-12.0104866027832</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>38.40325546264648</v>
+        <v>42.64474868774414</v>
       </c>
       <c r="B149" t="n">
-        <v>38.34479904174805</v>
+        <v>43.93447113037109</v>
       </c>
       <c r="C149" t="n">
-        <v>15.06896781921387</v>
+        <v>16.92523574829102</v>
       </c>
       <c r="D149" t="n">
-        <v>13.50422191619873</v>
+        <v>22.06405067443848</v>
       </c>
       <c r="E149" t="n">
-        <v>-7.638428688049316</v>
+        <v>0.7057218551635742</v>
       </c>
       <c r="F149" t="n">
-        <v>-19.13495254516602</v>
+        <v>-10.41178607940674</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>39.26570510864258</v>
+        <v>42.43977737426758</v>
       </c>
       <c r="B150" t="n">
-        <v>37.84822463989258</v>
+        <v>43.74440383911133</v>
       </c>
       <c r="C150" t="n">
-        <v>15.6413745880127</v>
+        <v>14.49453449249268</v>
       </c>
       <c r="D150" t="n">
-        <v>11.51968955993652</v>
+        <v>19.52980041503906</v>
       </c>
       <c r="E150" t="n">
-        <v>-9.483457565307617</v>
+        <v>0.2612495422363281</v>
       </c>
       <c r="F150" t="n">
-        <v>-18.25977897644043</v>
+        <v>-12.34909439086914</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>37.15988540649414</v>
+        <v>31.97126007080078</v>
       </c>
       <c r="B151" t="n">
-        <v>35.89216232299805</v>
+        <v>43.29787445068359</v>
       </c>
       <c r="C151" t="n">
-        <v>15.17648124694824</v>
+        <v>8.605599403381348</v>
       </c>
       <c r="D151" t="n">
-        <v>12.147292137146</v>
+        <v>15.90476322174072</v>
       </c>
       <c r="E151" t="n">
-        <v>-9.848466873168945</v>
+        <v>-2.015753269195557</v>
       </c>
       <c r="F151" t="n">
-        <v>-19.91792869567871</v>
+        <v>-11.82324314117432</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>38.69990539550781</v>
+        <v>31.37516593933105</v>
       </c>
       <c r="B152" t="n">
-        <v>37.22836303710938</v>
+        <v>42.91155624389648</v>
       </c>
       <c r="C152" t="n">
-        <v>16.36623954772949</v>
+        <v>5.970683097839355</v>
       </c>
       <c r="D152" t="n">
-        <v>12.14502143859863</v>
+        <v>14.0570707321167</v>
       </c>
       <c r="E152" t="n">
-        <v>-12.45666027069092</v>
+        <v>-3.485033512115479</v>
       </c>
       <c r="F152" t="n">
-        <v>-21.62565040588379</v>
+        <v>-13.02824783325195</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>38.62947845458984</v>
+        <v>30.61114311218262</v>
       </c>
       <c r="B153" t="n">
-        <v>38.1407356262207</v>
+        <v>40.99970626831055</v>
       </c>
       <c r="C153" t="n">
-        <v>17.10920333862305</v>
+        <v>5.993510246276855</v>
       </c>
       <c r="D153" t="n">
-        <v>13.91647052764893</v>
+        <v>14.02708530426025</v>
       </c>
       <c r="E153" t="n">
-        <v>-14.10729503631592</v>
+        <v>-5.807891845703125</v>
       </c>
       <c r="F153" t="n">
-        <v>-23.64313125610352</v>
+        <v>-15.28915977478027</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>40.02771377563477</v>
+        <v>29.6537036895752</v>
       </c>
       <c r="B154" t="n">
-        <v>36.3798828125</v>
+        <v>39.99518585205078</v>
       </c>
       <c r="C154" t="n">
-        <v>16.2931079864502</v>
+        <v>5.780819892883301</v>
       </c>
       <c r="D154" t="n">
-        <v>16.2705135345459</v>
+        <v>13.67957782745361</v>
       </c>
       <c r="E154" t="n">
-        <v>-14.92987823486328</v>
+        <v>-8.303143501281738</v>
       </c>
       <c r="F154" t="n">
-        <v>-24.83338165283203</v>
+        <v>-16.20796394348145</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>41.30998229980469</v>
+        <v>26.94940185546875</v>
       </c>
       <c r="B155" t="n">
-        <v>36.52048873901367</v>
+        <v>38.71350479125977</v>
       </c>
       <c r="C155" t="n">
-        <v>19.33915519714355</v>
+        <v>4.805041313171387</v>
       </c>
       <c r="D155" t="n">
-        <v>18.62896347045898</v>
+        <v>15.2206392288208</v>
       </c>
       <c r="E155" t="n">
-        <v>-18.910888671875</v>
+        <v>-9.688236236572266</v>
       </c>
       <c r="F155" t="n">
-        <v>-25.65201568603516</v>
+        <v>-16.26711845397949</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>41.9410514831543</v>
+        <v>25.65802192687988</v>
       </c>
       <c r="B156" t="n">
-        <v>35.14583969116211</v>
+        <v>36.93944931030273</v>
       </c>
       <c r="C156" t="n">
-        <v>20.8290958404541</v>
+        <v>4.893403053283691</v>
       </c>
       <c r="D156" t="n">
-        <v>19.71778297424316</v>
+        <v>17.30681037902832</v>
       </c>
       <c r="E156" t="n">
-        <v>-20.41687774658203</v>
+        <v>-11.50905323028564</v>
       </c>
       <c r="F156" t="n">
-        <v>-25.28211212158203</v>
+        <v>-16.60494422912598</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>42.81236267089844</v>
+        <v>25.18844604492188</v>
       </c>
       <c r="B157" t="n">
-        <v>35.19460678100586</v>
+        <v>35.99816131591797</v>
       </c>
       <c r="C157" t="n">
-        <v>23.69414520263672</v>
+        <v>4.284245491027832</v>
       </c>
       <c r="D157" t="n">
-        <v>22.44210624694824</v>
+        <v>17.42215919494629</v>
       </c>
       <c r="E157" t="n">
-        <v>-19.92022132873535</v>
+        <v>-12.11913299560547</v>
       </c>
       <c r="F157" t="n">
-        <v>-22.80292892456055</v>
+        <v>-16.291748046875</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>42.54785537719727</v>
+        <v>25.00638198852539</v>
       </c>
       <c r="B158" t="n">
-        <v>33.87714385986328</v>
+        <v>35.99734115600586</v>
       </c>
       <c r="C158" t="n">
-        <v>25.67413711547852</v>
+        <v>2.877554655075073</v>
       </c>
       <c r="D158" t="n">
-        <v>23.84738159179688</v>
+        <v>19.03038024902344</v>
       </c>
       <c r="E158" t="n">
-        <v>-17.75299835205078</v>
+        <v>-11.85879039764404</v>
       </c>
       <c r="F158" t="n">
-        <v>-20.48686599731445</v>
+        <v>-15.77921199798584</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>41.87357711791992</v>
+        <v>26.79990386962891</v>
       </c>
       <c r="B159" t="n">
-        <v>32.2120475769043</v>
+        <v>35.67469024658203</v>
       </c>
       <c r="C159" t="n">
-        <v>27.61631965637207</v>
+        <v>5.043341636657715</v>
       </c>
       <c r="D159" t="n">
-        <v>23.49324226379395</v>
+        <v>20.5753116607666</v>
       </c>
       <c r="E159" t="n">
-        <v>-14.57031440734863</v>
+        <v>-13.16796112060547</v>
       </c>
       <c r="F159" t="n">
-        <v>-20.13847732543945</v>
+        <v>-14.76644611358643</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>40.07920455932617</v>
+        <v>25.75861549377441</v>
       </c>
       <c r="B160" t="n">
-        <v>30.83370971679688</v>
+        <v>36.0088996887207</v>
       </c>
       <c r="C160" t="n">
-        <v>28.49485969543457</v>
+        <v>4.985228538513184</v>
       </c>
       <c r="D160" t="n">
-        <v>23.82087898254395</v>
+        <v>21.10804557800293</v>
       </c>
       <c r="E160" t="n">
-        <v>-10.95298862457275</v>
+        <v>-12.31924629211426</v>
       </c>
       <c r="F160" t="n">
-        <v>-16.2178840637207</v>
+        <v>-11.65879917144775</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>38.02321243286133</v>
+        <v>24.26194763183594</v>
       </c>
       <c r="B161" t="n">
-        <v>29.36182403564453</v>
+        <v>33.76523971557617</v>
       </c>
       <c r="C161" t="n">
-        <v>26.85256195068359</v>
+        <v>5.158713340759277</v>
       </c>
       <c r="D161" t="n">
-        <v>23.37789535522461</v>
+        <v>21.12664031982422</v>
       </c>
       <c r="E161" t="n">
-        <v>-6.705893516540527</v>
+        <v>-11.56260395050049</v>
       </c>
       <c r="F161" t="n">
-        <v>-14.85715293884277</v>
+        <v>-9.061450958251953</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>36.01914978027344</v>
+        <v>24.13119316101074</v>
       </c>
       <c r="B162" t="n">
-        <v>27.02153396606445</v>
+        <v>31.13975524902344</v>
       </c>
       <c r="C162" t="n">
-        <v>26.05087852478027</v>
+        <v>5.470789909362793</v>
       </c>
       <c r="D162" t="n">
-        <v>22.6981029510498</v>
+        <v>20.00394248962402</v>
       </c>
       <c r="E162" t="n">
-        <v>-4.832550525665283</v>
+        <v>-10.67556476593018</v>
       </c>
       <c r="F162" t="n">
-        <v>-12.31142139434814</v>
+        <v>-7.960689067840576</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>33.56678771972656</v>
+        <v>23.40485382080078</v>
       </c>
       <c r="B163" t="n">
-        <v>26.15570831298828</v>
+        <v>29.84380912780762</v>
       </c>
       <c r="C163" t="n">
-        <v>24.74829864501953</v>
+        <v>5.444518089294434</v>
       </c>
       <c r="D163" t="n">
-        <v>21.18897247314453</v>
+        <v>18.84264373779297</v>
       </c>
       <c r="E163" t="n">
-        <v>-3.675776958465576</v>
+        <v>-9.973987579345703</v>
       </c>
       <c r="F163" t="n">
-        <v>-11.50569725036621</v>
+        <v>-3.797191381454468</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>30.5892276763916</v>
+        <v>22.50801086425781</v>
       </c>
       <c r="B164" t="n">
-        <v>23.98070526123047</v>
+        <v>28.03312301635742</v>
       </c>
       <c r="C164" t="n">
-        <v>22.91854476928711</v>
+        <v>5.989768028259277</v>
       </c>
       <c r="D164" t="n">
-        <v>20.94578552246094</v>
+        <v>19.66451072692871</v>
       </c>
       <c r="E164" t="n">
-        <v>-3.671403169631958</v>
+        <v>-8.255806922912598</v>
       </c>
       <c r="F164" t="n">
-        <v>-10.51547145843506</v>
+        <v>-1.556069016456604</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>28.82774353027344</v>
+        <v>21.20139694213867</v>
       </c>
       <c r="B165" t="n">
-        <v>21.61293029785156</v>
+        <v>27.62612915039062</v>
       </c>
       <c r="C165" t="n">
-        <v>21.63616561889648</v>
+        <v>5.35802173614502</v>
       </c>
       <c r="D165" t="n">
-        <v>18.87555885314941</v>
+        <v>19.10927391052246</v>
       </c>
       <c r="E165" t="n">
-        <v>-3.438348770141602</v>
+        <v>-7.470250129699707</v>
       </c>
       <c r="F165" t="n">
-        <v>-9.45928955078125</v>
+        <v>-1.378168225288391</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>26.40094566345215</v>
+        <v>20.14396095275879</v>
       </c>
       <c r="B166" t="n">
-        <v>20.12634658813477</v>
+        <v>25.20609283447266</v>
       </c>
       <c r="C166" t="n">
-        <v>19.78035354614258</v>
+        <v>5.604002952575684</v>
       </c>
       <c r="D166" t="n">
-        <v>17.45161247253418</v>
+        <v>17.18393898010254</v>
       </c>
       <c r="E166" t="n">
-        <v>-3.170185089111328</v>
+        <v>-5.965624809265137</v>
       </c>
       <c r="F166" t="n">
-        <v>-8.32701301574707</v>
+        <v>-0.122130461037159</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>23.74470329284668</v>
+        <v>20.02825546264648</v>
       </c>
       <c r="B167" t="n">
-        <v>18.38947677612305</v>
+        <v>23.43610000610352</v>
       </c>
       <c r="C167" t="n">
-        <v>17.16292953491211</v>
+        <v>4.872603416442871</v>
       </c>
       <c r="D167" t="n">
-        <v>16.4110279083252</v>
+        <v>17.10421180725098</v>
       </c>
       <c r="E167" t="n">
-        <v>-2.10783863067627</v>
+        <v>-5.457824230194092</v>
       </c>
       <c r="F167" t="n">
-        <v>-8.476462364196777</v>
+        <v>1.008763670921326</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>21.76244163513184</v>
+        <v>18.71771049499512</v>
       </c>
       <c r="B168" t="n">
-        <v>16.64130401611328</v>
+        <v>22.19314956665039</v>
       </c>
       <c r="C168" t="n">
-        <v>16.31704902648926</v>
+        <v>5.985587120056152</v>
       </c>
       <c r="D168" t="n">
-        <v>14.99776649475098</v>
+        <v>17.00530242919922</v>
       </c>
       <c r="E168" t="n">
-        <v>-1.133328437805176</v>
+        <v>-5.57483959197998</v>
       </c>
       <c r="F168" t="n">
-        <v>-9.015512466430664</v>
+        <v>2.064848899841309</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>19.98827171325684</v>
+        <v>18.0135383605957</v>
       </c>
       <c r="B169" t="n">
-        <v>14.04121017456055</v>
+        <v>20.68726539611816</v>
       </c>
       <c r="C169" t="n">
-        <v>15.59915065765381</v>
+        <v>4.323332786560059</v>
       </c>
       <c r="D169" t="n">
-        <v>14.01570796966553</v>
+        <v>14.62887382507324</v>
       </c>
       <c r="E169" t="n">
-        <v>0.2670259475708008</v>
+        <v>-5.470122814178467</v>
       </c>
       <c r="F169" t="n">
-        <v>-7.995745658874512</v>
+        <v>2.828037261962891</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>17.22615242004395</v>
+        <v>17.41912269592285</v>
       </c>
       <c r="B170" t="n">
-        <v>12.62564468383789</v>
+        <v>19.1112174987793</v>
       </c>
       <c r="C170" t="n">
-        <v>14.20675277709961</v>
+        <v>3.697691679000854</v>
       </c>
       <c r="D170" t="n">
-        <v>13.04206657409668</v>
+        <v>14.00417995452881</v>
       </c>
       <c r="E170" t="n">
-        <v>0.7756814956665039</v>
+        <v>-6.037752628326416</v>
       </c>
       <c r="F170" t="n">
-        <v>-8.621555328369141</v>
+        <v>2.046622276306152</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>14.80602169036865</v>
+        <v>15.99081420898438</v>
       </c>
       <c r="B171" t="n">
-        <v>9.811216354370117</v>
+        <v>17.66439056396484</v>
       </c>
       <c r="C171" t="n">
-        <v>13.13183403015137</v>
+        <v>4.178042411804199</v>
       </c>
       <c r="D171" t="n">
-        <v>11.12950706481934</v>
+        <v>15.24643421173096</v>
       </c>
       <c r="E171" t="n">
-        <v>1.814016342163086</v>
+        <v>-5.917618274688721</v>
       </c>
       <c r="F171" t="n">
-        <v>-8.514591217041016</v>
+        <v>2.19804859161377</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>12.38873672485352</v>
+        <v>14.82215023040771</v>
       </c>
       <c r="B172" t="n">
-        <v>9.465437889099121</v>
+        <v>16.91817474365234</v>
       </c>
       <c r="C172" t="n">
-        <v>12.06722354888916</v>
+        <v>3.132351636886597</v>
       </c>
       <c r="D172" t="n">
-        <v>11.87602233886719</v>
+        <v>12.41879749298096</v>
       </c>
       <c r="E172" t="n">
-        <v>3.114897727966309</v>
+        <v>-6.369421005249023</v>
       </c>
       <c r="F172" t="n">
-        <v>-7.966396808624268</v>
+        <v>2.160575866699219</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>11.15559959411621</v>
+        <v>12.62150287628174</v>
       </c>
       <c r="B173" t="n">
-        <v>6.847249031066895</v>
+        <v>13.7260570526123</v>
       </c>
       <c r="C173" t="n">
-        <v>12.3712329864502</v>
+        <v>2.831902265548706</v>
       </c>
       <c r="D173" t="n">
-        <v>11.14869403839111</v>
+        <v>12.57962226867676</v>
       </c>
       <c r="E173" t="n">
-        <v>3.48252010345459</v>
+        <v>-5.974025726318359</v>
       </c>
       <c r="F173" t="n">
-        <v>-8.222627639770508</v>
+        <v>2.105218887329102</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>9.146547317504883</v>
+        <v>12.89182949066162</v>
       </c>
       <c r="B174" t="n">
-        <v>5.766797065734863</v>
+        <v>13.82608699798584</v>
       </c>
       <c r="C174" t="n">
-        <v>11.97144889831543</v>
+        <v>2.729595899581909</v>
       </c>
       <c r="D174" t="n">
-        <v>11.47702980041504</v>
+        <v>13.21210289001465</v>
       </c>
       <c r="E174" t="n">
-        <v>5.859041213989258</v>
+        <v>-6.720951080322266</v>
       </c>
       <c r="F174" t="n">
-        <v>-6.665465831756592</v>
+        <v>2.331036567687988</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>7.271013736724854</v>
+        <v>10.55345058441162</v>
       </c>
       <c r="B175" t="n">
-        <v>5.066216468811035</v>
+        <v>13.7185115814209</v>
       </c>
       <c r="C175" t="n">
-        <v>13.20944023132324</v>
+        <v>8.387703895568848</v>
       </c>
       <c r="D175" t="n">
-        <v>12.76426601409912</v>
+        <v>13.57830333709717</v>
       </c>
       <c r="E175" t="n">
-        <v>6.026102066040039</v>
+        <v>-5.252821445465088</v>
       </c>
       <c r="F175" t="n">
-        <v>-7.368050098419189</v>
+        <v>1.871373057365417</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>6.470224857330322</v>
+        <v>9.404035568237305</v>
       </c>
       <c r="B176" t="n">
-        <v>4.098834037780762</v>
+        <v>12.16229248046875</v>
       </c>
       <c r="C176" t="n">
-        <v>14.95466232299805</v>
+        <v>9.401915550231934</v>
       </c>
       <c r="D176" t="n">
-        <v>14.34445381164551</v>
+        <v>14.90681743621826</v>
       </c>
       <c r="E176" t="n">
-        <v>7.801933288574219</v>
+        <v>-7.483375072479248</v>
       </c>
       <c r="F176" t="n">
-        <v>-6.994024276733398</v>
+        <v>2.401467323303223</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>5.206844806671143</v>
+        <v>9.629246711730957</v>
       </c>
       <c r="B177" t="n">
-        <v>3.002306699752808</v>
+        <v>10.60704517364502</v>
       </c>
       <c r="C177" t="n">
-        <v>16.69012260437012</v>
+        <v>11.12008666992188</v>
       </c>
       <c r="D177" t="n">
-        <v>15.79114723205566</v>
+        <v>15.97028732299805</v>
       </c>
       <c r="E177" t="n">
-        <v>7.792773246765137</v>
+        <v>-10.95169734954834</v>
       </c>
       <c r="F177" t="n">
-        <v>-7.665769100189209</v>
+        <v>-0.3643317818641663</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>4.766832828521729</v>
+        <v>9.380805015563965</v>
       </c>
       <c r="B178" t="n">
-        <v>3.827545881271362</v>
+        <v>11.87106609344482</v>
       </c>
       <c r="C178" t="n">
-        <v>18.93465042114258</v>
+        <v>12.26807498931885</v>
       </c>
       <c r="D178" t="n">
-        <v>18.59258842468262</v>
+        <v>16.28140449523926</v>
       </c>
       <c r="E178" t="n">
-        <v>5.139706611633301</v>
+        <v>-16.50388717651367</v>
       </c>
       <c r="F178" t="n">
-        <v>-9.853647232055664</v>
+        <v>-2.673449993133545</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>4.64121675491333</v>
+        <v>10.1366548538208</v>
       </c>
       <c r="B179" t="n">
-        <v>4.104830741882324</v>
+        <v>10.29434490203857</v>
       </c>
       <c r="C179" t="n">
-        <v>21.36641120910645</v>
+        <v>15.7087230682373</v>
       </c>
       <c r="D179" t="n">
-        <v>21.41153526306152</v>
+        <v>19.09600257873535</v>
       </c>
       <c r="E179" t="n">
-        <v>-1.130520820617676</v>
+        <v>-20.99384689331055</v>
       </c>
       <c r="F179" t="n">
-        <v>-16.08995628356934</v>
+        <v>-7.56375789642334</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>5.962849140167236</v>
+        <v>8.911410331726074</v>
       </c>
       <c r="B180" t="n">
-        <v>5.091450691223145</v>
+        <v>11.16815567016602</v>
       </c>
       <c r="C180" t="n">
-        <v>24.16213989257812</v>
+        <v>18.23388862609863</v>
       </c>
       <c r="D180" t="n">
-        <v>24.96333312988281</v>
+        <v>21.54294967651367</v>
       </c>
       <c r="E180" t="n">
-        <v>-10.08875560760498</v>
+        <v>-23.98431777954102</v>
       </c>
       <c r="F180" t="n">
-        <v>-23.97243690490723</v>
+        <v>-14.60125255584717</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>6.663351535797119</v>
+        <v>9.638396263122559</v>
       </c>
       <c r="B181" t="n">
-        <v>7.102852821350098</v>
+        <v>11.0250997543335</v>
       </c>
       <c r="C181" t="n">
-        <v>29.87036323547363</v>
+        <v>21.11907196044922</v>
       </c>
       <c r="D181" t="n">
-        <v>29.13540267944336</v>
+        <v>25.19072341918945</v>
       </c>
       <c r="E181" t="n">
-        <v>-22.90121841430664</v>
+        <v>-27.36018371582031</v>
       </c>
       <c r="F181" t="n">
-        <v>-32.44542694091797</v>
+        <v>-22.68564796447754</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>8.749089241027832</v>
+        <v>10.01922798156738</v>
       </c>
       <c r="B182" t="n">
-        <v>8.466449737548828</v>
+        <v>11.26279067993164</v>
       </c>
       <c r="C182" t="n">
-        <v>33.95525741577148</v>
+        <v>25.23142051696777</v>
       </c>
       <c r="D182" t="n">
-        <v>32.79001235961914</v>
+        <v>28.22659492492676</v>
       </c>
       <c r="E182" t="n">
-        <v>-34.90949249267578</v>
+        <v>-31.10305786132812</v>
       </c>
       <c r="F182" t="n">
-        <v>-42.94750213623047</v>
+        <v>-33.02563095092773</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>11.15007209777832</v>
+        <v>12.80899429321289</v>
       </c>
       <c r="B183" t="n">
-        <v>10.16451644897461</v>
+        <v>12.3449535369873</v>
       </c>
       <c r="C183" t="n">
-        <v>39.12685394287109</v>
+        <v>29.23806571960449</v>
       </c>
       <c r="D183" t="n">
-        <v>37.57735443115234</v>
+        <v>33.44635391235352</v>
       </c>
       <c r="E183" t="n">
-        <v>-45.42497253417969</v>
+        <v>-33.9208869934082</v>
       </c>
       <c r="F183" t="n">
-        <v>-51.64890289306641</v>
+        <v>-40.93357086181641</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>13.95012092590332</v>
+        <v>14.28786945343018</v>
       </c>
       <c r="B184" t="n">
-        <v>14.35788822174072</v>
+        <v>13.66753387451172</v>
       </c>
       <c r="C184" t="n">
-        <v>43.62689971923828</v>
+        <v>34.13922882080078</v>
       </c>
       <c r="D184" t="n">
-        <v>42.21195983886719</v>
+        <v>37.39053344726562</v>
       </c>
       <c r="E184" t="n">
-        <v>-49.88677978515625</v>
+        <v>-35.08917236328125</v>
       </c>
       <c r="F184" t="n">
-        <v>-57.48871994018555</v>
+        <v>-50.76110458374023</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>17.35492897033691</v>
+        <v>16.93928146362305</v>
       </c>
       <c r="B185" t="n">
-        <v>16.50052642822266</v>
+        <v>16.21722221374512</v>
       </c>
       <c r="C185" t="n">
-        <v>48.98738861083984</v>
+        <v>38.18167114257812</v>
       </c>
       <c r="D185" t="n">
-        <v>45.95890808105469</v>
+        <v>41.90582275390625</v>
       </c>
       <c r="E185" t="n">
-        <v>-49.47509384155273</v>
+        <v>-36.23036193847656</v>
       </c>
       <c r="F185" t="n">
-        <v>-57.2581787109375</v>
+        <v>-55.90654373168945</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>20.15799903869629</v>
+        <v>19.07648468017578</v>
       </c>
       <c r="B186" t="n">
-        <v>20.48847770690918</v>
+        <v>18.27656936645508</v>
       </c>
       <c r="C186" t="n">
-        <v>52.31323623657227</v>
+        <v>41.41866302490234</v>
       </c>
       <c r="D186" t="n">
-        <v>49.16941070556641</v>
+        <v>46.52920150756836</v>
       </c>
       <c r="E186" t="n">
-        <v>-46.27280807495117</v>
+        <v>-35.57386016845703</v>
       </c>
       <c r="F186" t="n">
-        <v>-54.52724456787109</v>
+        <v>-57.01650619506836</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>24.30187034606934</v>
+        <v>22.4223575592041</v>
       </c>
       <c r="B187" t="n">
-        <v>23.44889259338379</v>
+        <v>20.93509292602539</v>
       </c>
       <c r="C187" t="n">
-        <v>55.43157958984375</v>
+        <v>45.13720321655273</v>
       </c>
       <c r="D187" t="n">
-        <v>52.90915298461914</v>
+        <v>49.87496948242188</v>
       </c>
       <c r="E187" t="n">
-        <v>-39.95475006103516</v>
+        <v>-35.11101913452148</v>
       </c>
       <c r="F187" t="n">
-        <v>-47.72573089599609</v>
+        <v>-57.28006362915039</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>27.39794540405273</v>
+        <v>25.60790252685547</v>
       </c>
       <c r="B188" t="n">
-        <v>27.42502021789551</v>
+        <v>23.61663436889648</v>
       </c>
       <c r="C188" t="n">
-        <v>57.99197387695312</v>
+        <v>47.78394317626953</v>
       </c>
       <c r="D188" t="n">
-        <v>55.02436447143555</v>
+        <v>50.94600677490234</v>
       </c>
       <c r="E188" t="n">
-        <v>-33.98805236816406</v>
+        <v>-30.8202018737793</v>
       </c>
       <c r="F188" t="n">
-        <v>-40.39043426513672</v>
+        <v>-54.70298385620117</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>30.69050025939941</v>
+        <v>28.35140800476074</v>
       </c>
       <c r="B189" t="n">
-        <v>29.95022773742676</v>
+        <v>26.89063453674316</v>
       </c>
       <c r="C189" t="n">
-        <v>59.21186065673828</v>
+        <v>48.20785140991211</v>
       </c>
       <c r="D189" t="n">
-        <v>55.54436111450195</v>
+        <v>54.20815277099609</v>
       </c>
       <c r="E189" t="n">
-        <v>-28.63790321350098</v>
+        <v>-28.14974403381348</v>
       </c>
       <c r="F189" t="n">
-        <v>-35.05709075927734</v>
+        <v>-48.53197479248047</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>32.91382598876953</v>
+        <v>31.12566375732422</v>
       </c>
       <c r="B190" t="n">
-        <v>32.61611175537109</v>
+        <v>29.25538635253906</v>
       </c>
       <c r="C190" t="n">
-        <v>55.03054046630859</v>
+        <v>48.65879058837891</v>
       </c>
       <c r="D190" t="n">
-        <v>53.93621444702148</v>
+        <v>54.85819625854492</v>
       </c>
       <c r="E190" t="n">
-        <v>-25.04359245300293</v>
+        <v>-24.07990837097168</v>
       </c>
       <c r="F190" t="n">
-        <v>-30.65853691101074</v>
+        <v>-41.61048889160156</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>35.47763442993164</v>
+        <v>32.76579284667969</v>
       </c>
       <c r="B191" t="n">
-        <v>34.91229248046875</v>
+        <v>31.8134765625</v>
       </c>
       <c r="C191" t="n">
-        <v>54.12065505981445</v>
+        <v>48.63368225097656</v>
       </c>
       <c r="D191" t="n">
-        <v>52.77020645141602</v>
+        <v>55.66545486450195</v>
       </c>
       <c r="E191" t="n">
-        <v>-22.85137748718262</v>
+        <v>-19.01872444152832</v>
       </c>
       <c r="F191" t="n">
-        <v>-27.25488090515137</v>
+        <v>-35.01533508300781</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>37.03249359130859</v>
+        <v>35.50767135620117</v>
       </c>
       <c r="B192" t="n">
-        <v>37.16546630859375</v>
+        <v>34.39073181152344</v>
       </c>
       <c r="C192" t="n">
-        <v>48.62637710571289</v>
+        <v>46.33493804931641</v>
       </c>
       <c r="D192" t="n">
-        <v>49.44350433349609</v>
+        <v>53.34215927124023</v>
       </c>
       <c r="E192" t="n">
-        <v>-19.90055847167969</v>
+        <v>-15.99666213989258</v>
       </c>
       <c r="F192" t="n">
-        <v>-25.46814918518066</v>
+        <v>-29.37209129333496</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>38.25940704345703</v>
+        <v>36.73295593261719</v>
       </c>
       <c r="B193" t="n">
-        <v>38.59347915649414</v>
+        <v>36.31753921508789</v>
       </c>
       <c r="C193" t="n">
-        <v>45.80945587158203</v>
+        <v>41.55649948120117</v>
       </c>
       <c r="D193" t="n">
-        <v>46.58007431030273</v>
+        <v>50.95049667358398</v>
       </c>
       <c r="E193" t="n">
-        <v>-18.07553291320801</v>
+        <v>-11.11227035522461</v>
       </c>
       <c r="F193" t="n">
-        <v>-22.84764099121094</v>
+        <v>-23.04222679138184</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>38.78191757202148</v>
+        <v>39.24832534790039</v>
       </c>
       <c r="B194" t="n">
-        <v>38.97128295898438</v>
+        <v>37.53654479980469</v>
       </c>
       <c r="C194" t="n">
-        <v>41.26070404052734</v>
+        <v>39.47817230224609</v>
       </c>
       <c r="D194" t="n">
-        <v>41.24222946166992</v>
+        <v>47.92900848388672</v>
       </c>
       <c r="E194" t="n">
-        <v>-15.64004230499268</v>
+        <v>-8.630102157592773</v>
       </c>
       <c r="F194" t="n">
-        <v>-22.3087272644043</v>
+        <v>-20.69695854187012</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>38.52663040161133</v>
+        <v>39.81624984741211</v>
       </c>
       <c r="B195" t="n">
-        <v>40.10572814941406</v>
+        <v>39.92276382446289</v>
       </c>
       <c r="C195" t="n">
-        <v>34.74000549316406</v>
+        <v>35.86420440673828</v>
       </c>
       <c r="D195" t="n">
-        <v>35.07912826538086</v>
+        <v>43.54874801635742</v>
       </c>
       <c r="E195" t="n">
-        <v>-14.122633934021</v>
+        <v>-4.678267002105713</v>
       </c>
       <c r="F195" t="n">
-        <v>-19.93790245056152</v>
+        <v>-16.29451370239258</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>38.74577713012695</v>
+        <v>42.31982040405273</v>
       </c>
       <c r="B196" t="n">
-        <v>38.81474304199219</v>
+        <v>40.52188491821289</v>
       </c>
       <c r="C196" t="n">
-        <v>28.67568969726562</v>
+        <v>32.792724609375</v>
       </c>
       <c r="D196" t="n">
-        <v>30.76195907592773</v>
+        <v>40.22384262084961</v>
       </c>
       <c r="E196" t="n">
-        <v>-12.14278888702393</v>
+        <v>-2.467272758483887</v>
       </c>
       <c r="F196" t="n">
-        <v>-19.67145729064941</v>
+        <v>-14.42383480072021</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>39.79319000244141</v>
+        <v>42.21105575561523</v>
       </c>
       <c r="B197" t="n">
-        <v>38.94931411743164</v>
+        <v>41.51411819458008</v>
       </c>
       <c r="C197" t="n">
-        <v>23.91394996643066</v>
+        <v>27.09594917297363</v>
       </c>
       <c r="D197" t="n">
-        <v>24.84218788146973</v>
+        <v>34.76276016235352</v>
       </c>
       <c r="E197" t="n">
-        <v>-9.980507850646973</v>
+        <v>-1.2473464012146</v>
       </c>
       <c r="F197" t="n">
-        <v>-20.17025756835938</v>
+        <v>-12.5947093963623</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>38.42719650268555</v>
+        <v>42.79973602294922</v>
       </c>
       <c r="B198" t="n">
-        <v>38.347900390625</v>
+        <v>41.99050140380859</v>
       </c>
       <c r="C198" t="n">
-        <v>19.35098838806152</v>
+        <v>24.6794548034668</v>
       </c>
       <c r="D198" t="n">
-        <v>19.49394989013672</v>
+        <v>30.01088333129883</v>
       </c>
       <c r="E198" t="n">
-        <v>-8.705069541931152</v>
+        <v>0.7432899475097656</v>
       </c>
       <c r="F198" t="n">
-        <v>-18.80542373657227</v>
+        <v>-10.3214750289917</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>38.66530227661133</v>
+        <v>40.76023483276367</v>
       </c>
       <c r="B199" t="n">
-        <v>38.16495132446289</v>
+        <v>42.13159942626953</v>
       </c>
       <c r="C199" t="n">
-        <v>17.31263732910156</v>
+        <v>19.13151359558105</v>
       </c>
       <c r="D199" t="n">
-        <v>15.32625675201416</v>
+        <v>25.43351554870605</v>
       </c>
       <c r="E199" t="n">
-        <v>-8.358205795288086</v>
+        <v>1.172606468200684</v>
       </c>
       <c r="F199" t="n">
-        <v>-17.98417663574219</v>
+        <v>-9.87773323059082</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>38.54621124267578</v>
+        <v>41.9149169921875</v>
       </c>
       <c r="B200" t="n">
-        <v>38.1910400390625</v>
+        <v>43.77721405029297</v>
       </c>
       <c r="C200" t="n">
-        <v>15.87545013427734</v>
+        <v>16.47451782226562</v>
       </c>
       <c r="D200" t="n">
-        <v>14.48744106292725</v>
+        <v>21.87544631958008</v>
       </c>
       <c r="E200" t="n">
-        <v>-7.435444355010986</v>
+        <v>1.355387687683105</v>
       </c>
       <c r="F200" t="n">
-        <v>-17.63889122009277</v>
+        <v>-8.456043243408203</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>39.47965621948242</v>
+        <v>41.54357528686523</v>
       </c>
       <c r="B201" t="n">
-        <v>37.59854125976562</v>
+        <v>43.34743881225586</v>
       </c>
       <c r="C201" t="n">
-        <v>16.32062530517578</v>
+        <v>14.3449010848999</v>
       </c>
       <c r="D201" t="n">
-        <v>12.33713722229004</v>
+        <v>19.50866317749023</v>
       </c>
       <c r="E201" t="n">
-        <v>-8.659452438354492</v>
+        <v>0.8947334289550781</v>
       </c>
       <c r="F201" t="n">
-        <v>-17.01746559143066</v>
+        <v>-10.30879592895508</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>37.78781509399414</v>
+        <v>31.30794715881348</v>
       </c>
       <c r="B202" t="n">
-        <v>36.2559700012207</v>
+        <v>43.07316970825195</v>
       </c>
       <c r="C202" t="n">
-        <v>16.29825973510742</v>
+        <v>8.62491512298584</v>
       </c>
       <c r="D202" t="n">
-        <v>13.11982822418213</v>
+        <v>16.03582954406738</v>
       </c>
       <c r="E202" t="n">
-        <v>-8.851315498352051</v>
+        <v>-1.504832744598389</v>
       </c>
       <c r="F202" t="n">
-        <v>-18.78726196289062</v>
+        <v>-9.883485794067383</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>38.90574645996094</v>
+        <v>30.63008689880371</v>
       </c>
       <c r="B203" t="n">
-        <v>36.78788375854492</v>
+        <v>42.58701324462891</v>
       </c>
       <c r="C203" t="n">
-        <v>17.48244476318359</v>
+        <v>6.38379955291748</v>
       </c>
       <c r="D203" t="n">
-        <v>13.81722164154053</v>
+        <v>14.25629043579102</v>
       </c>
       <c r="E203" t="n">
-        <v>-11.69062995910645</v>
+        <v>-2.938568115234375</v>
       </c>
       <c r="F203" t="n">
-        <v>-20.88721656799316</v>
+        <v>-11.48282241821289</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>38.91216659545898</v>
+        <v>30.09314918518066</v>
       </c>
       <c r="B204" t="n">
-        <v>37.52772903442383</v>
+        <v>40.93655776977539</v>
       </c>
       <c r="C204" t="n">
-        <v>18.28640365600586</v>
+        <v>6.143942832946777</v>
       </c>
       <c r="D204" t="n">
-        <v>14.8699312210083</v>
+        <v>14.12751007080078</v>
       </c>
       <c r="E204" t="n">
-        <v>-14.22677612304688</v>
+        <v>-5.773732662200928</v>
       </c>
       <c r="F204" t="n">
-        <v>-23.22781372070312</v>
+        <v>-14.15206718444824</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>37.45269012451172</v>
+        <v>38.17903900146484</v>
       </c>
       <c r="B205" t="n">
-        <v>37.45269012451172</v>
+        <v>38.17903900146484</v>
       </c>
       <c r="C205" t="n">
-        <v>37.45269012451172</v>
+        <v>38.17903900146484</v>
       </c>
       <c r="D205" t="n">
-        <v>37.45269012451172</v>
+        <v>38.17903900146484</v>
       </c>
       <c r="E205" t="n">
-        <v>37.45269012451172</v>
+        <v>38.17903900146484</v>
       </c>
       <c r="F205" t="n">
-        <v>37.45269012451172</v>
+        <v>38.17903900146484</v>
       </c>
     </row>
   </sheetData>
